--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ КИ/Копия дв 250626 бррсч пок ки от Боярко.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ КИ/Копия дв 250626 бррсч пок ки от Боярко.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC76C1DF-F49B-49BB-9815-EF00C95DDAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6E44F3-7717-4C5F-AFCF-C2BFE635BE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -486,7 +486,7 @@
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
     <numFmt numFmtId="165" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,6 +512,30 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -593,7 +617,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -612,9 +636,14 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3365,7 +3394,8 @@
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.42578125" customWidth="1"/>
     <col min="15" max="18" width="7" customWidth="1"/>
-    <col min="19" max="20" width="7" style="17" customWidth="1"/>
+    <col min="19" max="19" width="7" style="17" customWidth="1"/>
+    <col min="20" max="20" width="7" style="25" customWidth="1"/>
     <col min="21" max="21" width="7" customWidth="1"/>
     <col min="22" max="22" width="21" customWidth="1"/>
     <col min="23" max="24" width="5" customWidth="1"/>
@@ -3395,7 +3425,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="T1" s="18">
+      <c r="T1" s="19">
         <v>1.6</v>
       </c>
       <c r="U1" s="1"/>
@@ -3452,7 +3482,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="20"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -3545,7 +3575,7 @@
       <c r="S3" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="21" t="s">
         <v>147</v>
       </c>
       <c r="U3" s="7" t="s">
@@ -3630,7 +3660,7 @@
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1" t="s">
+      <c r="T4" s="20" t="s">
         <v>148</v>
       </c>
       <c r="U4" s="1"/>
@@ -3730,7 +3760,7 @@
         <f t="shared" si="0"/>
         <v>14993.911793999998</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="22">
         <f t="shared" si="0"/>
         <v>19317.94521759999</v>
       </c>
@@ -3843,7 +3873,7 @@
         <f>U6</f>
         <v>300</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6" s="23">
         <f>S6</f>
         <v>300</v>
       </c>
@@ -3957,7 +3987,7 @@
         <f t="shared" ref="S7:S8" si="3">U7</f>
         <v>200</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="23">
         <f t="shared" ref="T7:T70" si="4">S7</f>
         <v>200</v>
       </c>
@@ -4071,7 +4101,7 @@
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="T8" s="5">
+      <c r="T8" s="23">
         <f t="shared" si="4"/>
         <v>150</v>
       </c>
@@ -4185,7 +4215,7 @@
         <f t="shared" ref="S9:S70" si="8">R9</f>
         <v>0</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4296,7 +4326,7 @@
         <f>U10</f>
         <v>400</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="23">
         <f t="shared" si="4"/>
         <v>400</v>
       </c>
@@ -4408,7 +4438,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T11" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4514,7 +4544,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T12" s="5">
+      <c r="T12" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4622,7 +4652,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T13" s="5">
+      <c r="T13" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4733,7 +4763,7 @@
         <f t="shared" si="8"/>
         <v>485.44399999999985</v>
       </c>
-      <c r="T14" s="5">
+      <c r="T14" s="23">
         <f>S14*$T$1</f>
         <v>776.71039999999982</v>
       </c>
@@ -4844,7 +4874,7 @@
         <f t="shared" si="8"/>
         <v>1936.1357999999996</v>
       </c>
-      <c r="T15" s="5">
+      <c r="T15" s="23">
         <f>S15*$T$1</f>
         <v>3097.8172799999993</v>
       </c>
@@ -4955,7 +4985,7 @@
         <f t="shared" si="8"/>
         <v>25.891595999999975</v>
       </c>
-      <c r="T16" s="5">
+      <c r="T16" s="23">
         <f t="shared" si="4"/>
         <v>25.891595999999975</v>
       </c>
@@ -5066,7 +5096,7 @@
         <f t="shared" si="8"/>
         <v>150.06836599999994</v>
       </c>
-      <c r="T17" s="5">
+      <c r="T17" s="23">
         <f t="shared" si="4"/>
         <v>150.06836599999994</v>
       </c>
@@ -5177,7 +5207,7 @@
         <f t="shared" si="8"/>
         <v>52.293305999999994</v>
       </c>
-      <c r="T18" s="5">
+      <c r="T18" s="23">
         <f t="shared" si="4"/>
         <v>52.293305999999994</v>
       </c>
@@ -5283,7 +5313,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T19" s="5">
+      <c r="T19" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5394,7 +5424,7 @@
         <f>U20</f>
         <v>500</v>
       </c>
-      <c r="T20" s="5">
+      <c r="T20" s="23">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
@@ -5509,7 +5539,7 @@
         <f t="shared" si="8"/>
         <v>95.874999999999943</v>
       </c>
-      <c r="T21" s="5">
+      <c r="T21" s="23">
         <f t="shared" si="4"/>
         <v>95.874999999999943</v>
       </c>
@@ -5617,7 +5647,7 @@
         <f>U22</f>
         <v>200</v>
       </c>
-      <c r="T22" s="5">
+      <c r="T22" s="23">
         <f t="shared" si="4"/>
         <v>200</v>
       </c>
@@ -5729,7 +5759,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T23" s="5">
+      <c r="T23" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5840,7 +5870,7 @@
         <f>U24</f>
         <v>555</v>
       </c>
-      <c r="T24" s="5">
+      <c r="T24" s="23">
         <f t="shared" si="4"/>
         <v>555</v>
       </c>
@@ -5952,7 +5982,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T25" s="5">
+      <c r="T25" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6060,7 +6090,7 @@
         <f t="shared" ref="S26:S27" si="10">U26</f>
         <v>580</v>
       </c>
-      <c r="T26" s="5">
+      <c r="T26" s="23">
         <f t="shared" si="4"/>
         <v>580</v>
       </c>
@@ -6177,7 +6207,7 @@
         <f t="shared" si="10"/>
         <v>400</v>
       </c>
-      <c r="T27" s="5">
+      <c r="T27" s="23">
         <f t="shared" si="4"/>
         <v>400</v>
       </c>
@@ -6287,7 +6317,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T28" s="5">
+      <c r="T28" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6398,7 +6428,7 @@
         <f t="shared" si="8"/>
         <v>99.110199999999992</v>
       </c>
-      <c r="T29" s="5">
+      <c r="T29" s="23">
         <f t="shared" si="4"/>
         <v>99.110199999999992</v>
       </c>
@@ -6506,7 +6536,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T30" s="5">
+      <c r="T30" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6610,7 +6640,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T31" s="5">
+      <c r="T31" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6721,7 +6751,7 @@
         <f t="shared" si="8"/>
         <v>955.68399999999929</v>
       </c>
-      <c r="T32" s="5">
+      <c r="T32" s="23">
         <f>S32*$T$1</f>
         <v>1529.094399999999</v>
       </c>
@@ -6832,7 +6862,7 @@
         <f t="shared" si="8"/>
         <v>221.90000000000009</v>
       </c>
-      <c r="T33" s="5">
+      <c r="T33" s="23">
         <f t="shared" si="4"/>
         <v>221.90000000000009</v>
       </c>
@@ -6943,7 +6973,7 @@
         <f t="shared" si="8"/>
         <v>584.57999999999993</v>
       </c>
-      <c r="T34" s="5">
+      <c r="T34" s="23">
         <f>S34*$T$1</f>
         <v>935.32799999999997</v>
       </c>
@@ -7051,7 +7081,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T35" s="5">
+      <c r="T35" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -7162,7 +7192,7 @@
         <f t="shared" si="8"/>
         <v>39.332399999999993</v>
       </c>
-      <c r="T36" s="5">
+      <c r="T36" s="23">
         <f t="shared" si="4"/>
         <v>39.332399999999993</v>
       </c>
@@ -7268,7 +7298,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T37" s="5">
+      <c r="T37" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -7374,7 +7404,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T38" s="5">
+      <c r="T38" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -7485,7 +7515,7 @@
         <f t="shared" si="8"/>
         <v>64.685599999999994</v>
       </c>
-      <c r="T39" s="5">
+      <c r="T39" s="23">
         <f t="shared" si="4"/>
         <v>64.685599999999994</v>
       </c>
@@ -7596,7 +7626,7 @@
         <f t="shared" si="8"/>
         <v>41.800000000000011</v>
       </c>
-      <c r="T40" s="5">
+      <c r="T40" s="23">
         <f t="shared" si="4"/>
         <v>41.800000000000011</v>
       </c>
@@ -7707,7 +7737,7 @@
         <f t="shared" si="8"/>
         <v>56.961999999999989</v>
       </c>
-      <c r="T41" s="5">
+      <c r="T41" s="23">
         <f t="shared" si="4"/>
         <v>56.961999999999989</v>
       </c>
@@ -7815,7 +7845,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T42" s="5">
+      <c r="T42" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -7923,7 +7953,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T43" s="5">
+      <c r="T43" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -8031,7 +8061,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T44" s="5">
+      <c r="T44" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -8142,7 +8172,7 @@
         <f t="shared" si="8"/>
         <v>233</v>
       </c>
-      <c r="T45" s="5">
+      <c r="T45" s="23">
         <f t="shared" si="4"/>
         <v>233</v>
       </c>
@@ -8250,7 +8280,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T46" s="5">
+      <c r="T46" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -8361,7 +8391,7 @@
         <f>U47</f>
         <v>150</v>
       </c>
-      <c r="T47" s="5">
+      <c r="T47" s="23">
         <f t="shared" si="4"/>
         <v>150</v>
       </c>
@@ -8476,7 +8506,7 @@
         <f t="shared" si="8"/>
         <v>63.557799999999929</v>
       </c>
-      <c r="T48" s="5">
+      <c r="T48" s="23">
         <f t="shared" si="4"/>
         <v>63.557799999999929</v>
       </c>
@@ -8587,7 +8617,7 @@
         <f>U49</f>
         <v>100</v>
       </c>
-      <c r="T49" s="5">
+      <c r="T49" s="23">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
@@ -8700,7 +8730,7 @@
         <f t="shared" si="8"/>
         <v>123.37599999999998</v>
       </c>
-      <c r="T50" s="5">
+      <c r="T50" s="23">
         <f t="shared" si="4"/>
         <v>123.37599999999998</v>
       </c>
@@ -8811,7 +8841,7 @@
         <f t="shared" si="8"/>
         <v>27.930000000000021</v>
       </c>
-      <c r="T51" s="5">
+      <c r="T51" s="23">
         <f t="shared" si="4"/>
         <v>27.930000000000021</v>
       </c>
@@ -8922,7 +8952,7 @@
         <f t="shared" ref="S52:S55" si="12">U52</f>
         <v>50</v>
       </c>
-      <c r="T52" s="5">
+      <c r="T52" s="23">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
@@ -9032,7 +9062,7 @@
         <f t="shared" si="12"/>
         <v>200</v>
       </c>
-      <c r="T53" s="5">
+      <c r="T53" s="23">
         <f t="shared" si="4"/>
         <v>200</v>
       </c>
@@ -9145,7 +9175,7 @@
         <f t="shared" si="12"/>
         <v>120</v>
       </c>
-      <c r="T54" s="5">
+      <c r="T54" s="23">
         <f t="shared" si="4"/>
         <v>120</v>
       </c>
@@ -9258,7 +9288,7 @@
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T55" s="5">
+      <c r="T55" s="23">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
@@ -9368,7 +9398,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T56" s="5">
+      <c r="T56" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9476,7 +9506,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T57" s="5">
+      <c r="T57" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9585,7 +9615,7 @@
         <f t="shared" si="8"/>
         <v>36.29478799999999</v>
       </c>
-      <c r="T58" s="5">
+      <c r="T58" s="23">
         <f t="shared" si="4"/>
         <v>36.29478799999999</v>
       </c>
@@ -9694,7 +9724,7 @@
         <f>U59</f>
         <v>40</v>
       </c>
-      <c r="T59" s="5">
+      <c r="T59" s="23">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
@@ -9804,7 +9834,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T60" s="5">
+      <c r="T60" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -9915,7 +9945,7 @@
         <f t="shared" si="8"/>
         <v>15.927999999999997</v>
       </c>
-      <c r="T61" s="5">
+      <c r="T61" s="23">
         <f t="shared" si="4"/>
         <v>15.927999999999997</v>
       </c>
@@ -10026,7 +10056,7 @@
         <f t="shared" si="8"/>
         <v>100.94923999999999</v>
       </c>
-      <c r="T62" s="5">
+      <c r="T62" s="23">
         <f t="shared" si="4"/>
         <v>100.94923999999999</v>
       </c>
@@ -10137,7 +10167,7 @@
         <f t="shared" si="8"/>
         <v>96.751791999999938</v>
       </c>
-      <c r="T63" s="5">
+      <c r="T63" s="23">
         <f t="shared" si="4"/>
         <v>96.751791999999938</v>
       </c>
@@ -10245,7 +10275,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T64" s="5">
+      <c r="T64" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -10353,7 +10383,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T65" s="5">
+      <c r="T65" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -10461,7 +10491,7 @@
         <f>U66</f>
         <v>200</v>
       </c>
-      <c r="T66" s="5">
+      <c r="T66" s="23">
         <f t="shared" si="4"/>
         <v>200</v>
       </c>
@@ -10573,7 +10603,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T67" s="5">
+      <c r="T67" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -10681,7 +10711,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T68" s="5">
+      <c r="T68" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -10792,7 +10822,7 @@
         <f>U69</f>
         <v>100</v>
       </c>
-      <c r="T69" s="5">
+      <c r="T69" s="23">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
@@ -10905,7 +10935,7 @@
         <f t="shared" si="8"/>
         <v>40.600000000000023</v>
       </c>
-      <c r="T70" s="5">
+      <c r="T70" s="23">
         <f t="shared" si="4"/>
         <v>40.600000000000023</v>
       </c>
@@ -11016,7 +11046,7 @@
         <f>U71</f>
         <v>100</v>
       </c>
-      <c r="T71" s="5">
+      <c r="T71" s="23">
         <f t="shared" ref="T71:T111" si="16">S71</f>
         <v>100</v>
       </c>
@@ -11129,7 +11159,7 @@
         <f t="shared" ref="S72:S111" si="20">R72</f>
         <v>47.399999999999977</v>
       </c>
-      <c r="T72" s="5">
+      <c r="T72" s="23">
         <f t="shared" si="16"/>
         <v>47.399999999999977</v>
       </c>
@@ -11240,7 +11270,7 @@
         <f>U73</f>
         <v>40</v>
       </c>
-      <c r="T73" s="5">
+      <c r="T73" s="23">
         <f t="shared" si="16"/>
         <v>40</v>
       </c>
@@ -11350,7 +11380,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T74" s="5">
+      <c r="T74" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -11458,7 +11488,7 @@
       <c r="S75" s="5">
         <v>50</v>
       </c>
-      <c r="T75" s="5">
+      <c r="T75" s="23">
         <f t="shared" si="16"/>
         <v>50</v>
       </c>
@@ -11568,7 +11598,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T76" s="5">
+      <c r="T76" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -11679,7 +11709,7 @@
         <f>U77</f>
         <v>500</v>
       </c>
-      <c r="T77" s="5">
+      <c r="T77" s="23">
         <f t="shared" si="16"/>
         <v>500</v>
       </c>
@@ -11794,7 +11824,7 @@
         <f t="shared" si="20"/>
         <v>988.36498599999902</v>
       </c>
-      <c r="T78" s="5">
+      <c r="T78" s="23">
         <f t="shared" ref="T78:T80" si="21">S78*$T$1</f>
         <v>1581.3839775999986</v>
       </c>
@@ -11905,7 +11935,7 @@
         <f>U79</f>
         <v>1100</v>
       </c>
-      <c r="T79" s="5">
+      <c r="T79" s="23">
         <f t="shared" si="21"/>
         <v>1760</v>
       </c>
@@ -12018,7 +12048,7 @@
         <f t="shared" si="20"/>
         <v>314.84691999999995</v>
       </c>
-      <c r="T80" s="5">
+      <c r="T80" s="23">
         <f t="shared" si="21"/>
         <v>503.75507199999993</v>
       </c>
@@ -12126,7 +12156,7 @@
         <f t="shared" ref="S81:S84" si="22">U81</f>
         <v>45</v>
       </c>
-      <c r="T81" s="5">
+      <c r="T81" s="23">
         <f t="shared" si="16"/>
         <v>45</v>
       </c>
@@ -12235,7 +12265,7 @@
         <f t="shared" si="22"/>
         <v>45</v>
       </c>
-      <c r="T82" s="5">
+      <c r="T82" s="23">
         <f t="shared" si="16"/>
         <v>45</v>
       </c>
@@ -12345,7 +12375,7 @@
         <f t="shared" si="22"/>
         <v>45</v>
       </c>
-      <c r="T83" s="5">
+      <c r="T83" s="23">
         <f t="shared" si="16"/>
         <v>45</v>
       </c>
@@ -12451,7 +12481,7 @@
         <f t="shared" si="22"/>
         <v>45</v>
       </c>
-      <c r="T84" s="5">
+      <c r="T84" s="23">
         <f t="shared" si="16"/>
         <v>45</v>
       </c>
@@ -12561,7 +12591,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T85" s="5">
+      <c r="T85" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -12672,7 +12702,7 @@
         <f>U86</f>
         <v>35</v>
       </c>
-      <c r="T86" s="19">
+      <c r="T86" s="24">
         <v>0</v>
       </c>
       <c r="U86" s="14">
@@ -12702,7 +12732,7 @@
       <c r="AC86" s="1">
         <v>13.6</v>
       </c>
-      <c r="AD86" s="20" t="s">
+      <c r="AD86" s="18" t="s">
         <v>149</v>
       </c>
       <c r="AE86" s="1">
@@ -12786,7 +12816,7 @@
         <f t="shared" si="20"/>
         <v>19</v>
       </c>
-      <c r="T87" s="5">
+      <c r="T87" s="23">
         <f t="shared" si="16"/>
         <v>19</v>
       </c>
@@ -12896,7 +12926,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T88" s="5">
+      <c r="T88" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -13004,7 +13034,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T89" s="5">
+      <c r="T89" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -13115,7 +13145,7 @@
         <f t="shared" si="20"/>
         <v>26.600000000000023</v>
       </c>
-      <c r="T90" s="5">
+      <c r="T90" s="23">
         <f t="shared" si="16"/>
         <v>26.600000000000023</v>
       </c>
@@ -13224,7 +13254,7 @@
         <f t="shared" si="20"/>
         <v>50.801999999999964</v>
       </c>
-      <c r="T91" s="5">
+      <c r="T91" s="23">
         <f t="shared" si="16"/>
         <v>50.801999999999964</v>
       </c>
@@ -13330,7 +13360,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T92" s="5">
+      <c r="T92" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -13441,7 +13471,7 @@
         <f t="shared" ref="S93:S97" si="23">U93</f>
         <v>200</v>
       </c>
-      <c r="T93" s="5">
+      <c r="T93" s="23">
         <f t="shared" si="16"/>
         <v>200</v>
       </c>
@@ -13555,7 +13585,7 @@
         <f t="shared" si="23"/>
         <v>100</v>
       </c>
-      <c r="T94" s="5">
+      <c r="T94" s="23">
         <f t="shared" si="16"/>
         <v>100</v>
       </c>
@@ -13661,7 +13691,7 @@
         <f t="shared" si="23"/>
         <v>40</v>
       </c>
-      <c r="T95" s="5">
+      <c r="T95" s="23">
         <f t="shared" si="16"/>
         <v>40</v>
       </c>
@@ -13778,7 +13808,7 @@
         <f t="shared" si="23"/>
         <v>500</v>
       </c>
-      <c r="T96" s="5">
+      <c r="T96" s="23">
         <f t="shared" ref="T96:T97" si="24">S96*$T$1</f>
         <v>800</v>
       </c>
@@ -13891,7 +13921,7 @@
         <f t="shared" si="23"/>
         <v>400</v>
       </c>
-      <c r="T97" s="5">
+      <c r="T97" s="23">
         <f t="shared" si="24"/>
         <v>640</v>
       </c>
@@ -13999,7 +14029,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T98" s="5">
+      <c r="T98" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -14105,7 +14135,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T99" s="5">
+      <c r="T99" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -14213,7 +14243,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T100" s="5">
+      <c r="T100" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -14326,7 +14356,7 @@
         <f>U101</f>
         <v>150</v>
       </c>
-      <c r="T101" s="5">
+      <c r="T101" s="23">
         <f t="shared" si="16"/>
         <v>150</v>
       </c>
@@ -14438,7 +14468,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T102" s="5">
+      <c r="T102" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -14549,7 +14579,7 @@
         <f>U103</f>
         <v>150</v>
       </c>
-      <c r="T103" s="5">
+      <c r="T103" s="23">
         <f t="shared" si="16"/>
         <v>150</v>
       </c>
@@ -14662,7 +14692,7 @@
         <f t="shared" si="20"/>
         <v>163.74800000000005</v>
       </c>
-      <c r="T104" s="5">
+      <c r="T104" s="23">
         <f t="shared" si="16"/>
         <v>163.74800000000005</v>
       </c>
@@ -14768,7 +14798,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T105" s="5">
+      <c r="T105" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -14876,7 +14906,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T106" s="5">
+      <c r="T106" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -14987,7 +15017,7 @@
         <f>U107</f>
         <v>25</v>
       </c>
-      <c r="T107" s="5">
+      <c r="T107" s="23">
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
@@ -15088,7 +15118,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T108" s="5">
+      <c r="T108" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -15186,7 +15216,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T109" s="5">
+      <c r="T109" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -15284,7 +15314,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T110" s="5">
+      <c r="T110" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -15382,7 +15412,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="T111" s="5">
+      <c r="T111" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -15458,7 +15488,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
-      <c r="T112" s="1"/>
+      <c r="T112" s="20"/>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
@@ -15513,7 +15543,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
-      <c r="T113" s="1"/>
+      <c r="T113" s="20"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
@@ -15568,7 +15598,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
-      <c r="T114" s="1"/>
+      <c r="T114" s="20"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
@@ -15623,7 +15653,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
-      <c r="T115" s="1"/>
+      <c r="T115" s="20"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
@@ -15678,7 +15708,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
-      <c r="T116" s="1"/>
+      <c r="T116" s="20"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
@@ -15733,7 +15763,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
-      <c r="T117" s="1"/>
+      <c r="T117" s="20"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
@@ -15788,7 +15818,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
-      <c r="T118" s="1"/>
+      <c r="T118" s="20"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
@@ -15843,7 +15873,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
-      <c r="T119" s="1"/>
+      <c r="T119" s="20"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
@@ -15898,7 +15928,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
-      <c r="T120" s="1"/>
+      <c r="T120" s="20"/>
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
@@ -15953,7 +15983,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
-      <c r="T121" s="1"/>
+      <c r="T121" s="20"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
@@ -16008,7 +16038,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
+      <c r="T122" s="20"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
@@ -16063,7 +16093,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
+      <c r="T123" s="20"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
@@ -16118,7 +16148,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
+      <c r="T124" s="20"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
@@ -16173,7 +16203,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
+      <c r="T125" s="20"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
@@ -16228,7 +16258,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
+      <c r="T126" s="20"/>
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
@@ -16283,7 +16313,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
-      <c r="T127" s="1"/>
+      <c r="T127" s="20"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
@@ -16338,7 +16368,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
-      <c r="T128" s="1"/>
+      <c r="T128" s="20"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
@@ -16393,7 +16423,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
-      <c r="T129" s="1"/>
+      <c r="T129" s="20"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
@@ -16448,7 +16478,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
+      <c r="T130" s="20"/>
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
@@ -16503,7 +16533,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
+      <c r="T131" s="20"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
@@ -16558,7 +16588,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
-      <c r="T132" s="1"/>
+      <c r="T132" s="20"/>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
@@ -16613,7 +16643,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
-      <c r="T133" s="1"/>
+      <c r="T133" s="20"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
@@ -16668,7 +16698,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
-      <c r="T134" s="1"/>
+      <c r="T134" s="20"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
@@ -16723,7 +16753,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
-      <c r="T135" s="1"/>
+      <c r="T135" s="20"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
@@ -16778,7 +16808,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
-      <c r="T136" s="1"/>
+      <c r="T136" s="20"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
@@ -16833,7 +16863,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
-      <c r="T137" s="1"/>
+      <c r="T137" s="20"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
@@ -16888,7 +16918,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
-      <c r="T138" s="1"/>
+      <c r="T138" s="20"/>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
@@ -16943,7 +16973,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
-      <c r="T139" s="1"/>
+      <c r="T139" s="20"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
@@ -16998,7 +17028,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
-      <c r="T140" s="1"/>
+      <c r="T140" s="20"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
@@ -17053,7 +17083,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
-      <c r="T141" s="1"/>
+      <c r="T141" s="20"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
@@ -17108,7 +17138,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
-      <c r="T142" s="1"/>
+      <c r="T142" s="20"/>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
@@ -17163,7 +17193,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
-      <c r="T143" s="1"/>
+      <c r="T143" s="20"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
@@ -17218,7 +17248,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
-      <c r="T144" s="1"/>
+      <c r="T144" s="20"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
@@ -17273,7 +17303,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
-      <c r="T145" s="1"/>
+      <c r="T145" s="20"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
@@ -17328,7 +17358,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
-      <c r="T146" s="1"/>
+      <c r="T146" s="20"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
@@ -17383,7 +17413,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
-      <c r="T147" s="1"/>
+      <c r="T147" s="20"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
@@ -17438,7 +17468,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
-      <c r="T148" s="1"/>
+      <c r="T148" s="20"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
@@ -17493,7 +17523,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
-      <c r="T149" s="1"/>
+      <c r="T149" s="20"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
@@ -17548,7 +17578,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
-      <c r="T150" s="1"/>
+      <c r="T150" s="20"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
@@ -17603,7 +17633,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
-      <c r="T151" s="1"/>
+      <c r="T151" s="20"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
@@ -17658,7 +17688,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
-      <c r="T152" s="1"/>
+      <c r="T152" s="20"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -17713,7 +17743,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
+      <c r="T153" s="20"/>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
@@ -17768,7 +17798,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
-      <c r="T154" s="1"/>
+      <c r="T154" s="20"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
@@ -17823,7 +17853,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
-      <c r="T155" s="1"/>
+      <c r="T155" s="20"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
@@ -17878,7 +17908,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
-      <c r="T156" s="1"/>
+      <c r="T156" s="20"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
@@ -17933,7 +17963,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
-      <c r="T157" s="1"/>
+      <c r="T157" s="20"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
@@ -17988,7 +18018,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
-      <c r="T158" s="1"/>
+      <c r="T158" s="20"/>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
@@ -18043,7 +18073,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
-      <c r="T159" s="1"/>
+      <c r="T159" s="20"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
@@ -18098,7 +18128,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
-      <c r="T160" s="1"/>
+      <c r="T160" s="20"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
@@ -18153,7 +18183,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
-      <c r="T161" s="1"/>
+      <c r="T161" s="20"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
@@ -18208,7 +18238,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
-      <c r="T162" s="1"/>
+      <c r="T162" s="20"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
@@ -18263,7 +18293,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
-      <c r="T163" s="1"/>
+      <c r="T163" s="20"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
@@ -18318,7 +18348,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
-      <c r="T164" s="1"/>
+      <c r="T164" s="20"/>
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
@@ -18373,7 +18403,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
-      <c r="T165" s="1"/>
+      <c r="T165" s="20"/>
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
@@ -18428,7 +18458,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
-      <c r="T166" s="1"/>
+      <c r="T166" s="20"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
@@ -18483,7 +18513,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
-      <c r="T167" s="1"/>
+      <c r="T167" s="20"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
@@ -18538,7 +18568,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
-      <c r="T168" s="1"/>
+      <c r="T168" s="20"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
@@ -18593,7 +18623,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
-      <c r="T169" s="1"/>
+      <c r="T169" s="20"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
@@ -18648,7 +18678,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
-      <c r="T170" s="1"/>
+      <c r="T170" s="20"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
@@ -18703,7 +18733,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
-      <c r="T171" s="1"/>
+      <c r="T171" s="20"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
@@ -18758,7 +18788,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
-      <c r="T172" s="1"/>
+      <c r="T172" s="20"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
@@ -18813,7 +18843,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
-      <c r="T173" s="1"/>
+      <c r="T173" s="20"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
@@ -18868,7 +18898,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
-      <c r="T174" s="1"/>
+      <c r="T174" s="20"/>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
@@ -18923,7 +18953,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
-      <c r="T175" s="1"/>
+      <c r="T175" s="20"/>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
@@ -18978,7 +19008,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
-      <c r="T176" s="1"/>
+      <c r="T176" s="20"/>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
@@ -19033,7 +19063,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
-      <c r="T177" s="1"/>
+      <c r="T177" s="20"/>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
@@ -19088,7 +19118,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
-      <c r="T178" s="1"/>
+      <c r="T178" s="20"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
@@ -19143,7 +19173,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
-      <c r="T179" s="1"/>
+      <c r="T179" s="20"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
@@ -19198,7 +19228,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
-      <c r="T180" s="1"/>
+      <c r="T180" s="20"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
@@ -19253,7 +19283,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
-      <c r="T181" s="1"/>
+      <c r="T181" s="20"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
@@ -19308,7 +19338,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
-      <c r="T182" s="1"/>
+      <c r="T182" s="20"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
@@ -19363,7 +19393,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
-      <c r="T183" s="1"/>
+      <c r="T183" s="20"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
@@ -19418,7 +19448,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
-      <c r="T184" s="1"/>
+      <c r="T184" s="20"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
@@ -19473,7 +19503,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
-      <c r="T185" s="1"/>
+      <c r="T185" s="20"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
@@ -19528,7 +19558,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
-      <c r="T186" s="1"/>
+      <c r="T186" s="20"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
@@ -19583,7 +19613,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
-      <c r="T187" s="1"/>
+      <c r="T187" s="20"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
@@ -19638,7 +19668,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
-      <c r="T188" s="1"/>
+      <c r="T188" s="20"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
@@ -19693,7 +19723,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
-      <c r="T189" s="1"/>
+      <c r="T189" s="20"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
@@ -19748,7 +19778,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
-      <c r="T190" s="1"/>
+      <c r="T190" s="20"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
@@ -19803,7 +19833,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
-      <c r="T191" s="1"/>
+      <c r="T191" s="20"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
@@ -19858,7 +19888,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
-      <c r="T192" s="1"/>
+      <c r="T192" s="20"/>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
@@ -19913,7 +19943,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
-      <c r="T193" s="1"/>
+      <c r="T193" s="20"/>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
@@ -19968,7 +19998,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
-      <c r="T194" s="1"/>
+      <c r="T194" s="20"/>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
@@ -20023,7 +20053,7 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
-      <c r="T195" s="1"/>
+      <c r="T195" s="20"/>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
@@ -20078,7 +20108,7 @@
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
-      <c r="T196" s="1"/>
+      <c r="T196" s="20"/>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
@@ -20133,7 +20163,7 @@
       <c r="Q197" s="1"/>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
-      <c r="T197" s="1"/>
+      <c r="T197" s="20"/>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
@@ -20188,7 +20218,7 @@
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
-      <c r="T198" s="1"/>
+      <c r="T198" s="20"/>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
@@ -20243,7 +20273,7 @@
       <c r="Q199" s="1"/>
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
-      <c r="T199" s="1"/>
+      <c r="T199" s="20"/>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
@@ -20298,7 +20328,7 @@
       <c r="Q200" s="1"/>
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
-      <c r="T200" s="1"/>
+      <c r="T200" s="20"/>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
@@ -20353,7 +20383,7 @@
       <c r="Q201" s="1"/>
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
-      <c r="T201" s="1"/>
+      <c r="T201" s="20"/>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
@@ -20408,7 +20438,7 @@
       <c r="Q202" s="1"/>
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
-      <c r="T202" s="1"/>
+      <c r="T202" s="20"/>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
@@ -20463,7 +20493,7 @@
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
-      <c r="T203" s="1"/>
+      <c r="T203" s="20"/>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
@@ -20518,7 +20548,7 @@
       <c r="Q204" s="1"/>
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
-      <c r="T204" s="1"/>
+      <c r="T204" s="20"/>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
@@ -20573,7 +20603,7 @@
       <c r="Q205" s="1"/>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
-      <c r="T205" s="1"/>
+      <c r="T205" s="20"/>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
@@ -20628,7 +20658,7 @@
       <c r="Q206" s="1"/>
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
-      <c r="T206" s="1"/>
+      <c r="T206" s="20"/>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
@@ -20683,7 +20713,7 @@
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
-      <c r="T207" s="1"/>
+      <c r="T207" s="20"/>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
@@ -20738,7 +20768,7 @@
       <c r="Q208" s="1"/>
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
-      <c r="T208" s="1"/>
+      <c r="T208" s="20"/>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
@@ -20793,7 +20823,7 @@
       <c r="Q209" s="1"/>
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
-      <c r="T209" s="1"/>
+      <c r="T209" s="20"/>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
@@ -20848,7 +20878,7 @@
       <c r="Q210" s="1"/>
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
-      <c r="T210" s="1"/>
+      <c r="T210" s="20"/>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
@@ -20903,7 +20933,7 @@
       <c r="Q211" s="1"/>
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
-      <c r="T211" s="1"/>
+      <c r="T211" s="20"/>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
@@ -20958,7 +20988,7 @@
       <c r="Q212" s="1"/>
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
-      <c r="T212" s="1"/>
+      <c r="T212" s="20"/>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
@@ -21013,7 +21043,7 @@
       <c r="Q213" s="1"/>
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
-      <c r="T213" s="1"/>
+      <c r="T213" s="20"/>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
@@ -21068,7 +21098,7 @@
       <c r="Q214" s="1"/>
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
-      <c r="T214" s="1"/>
+      <c r="T214" s="20"/>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
@@ -21123,7 +21153,7 @@
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
+      <c r="T215" s="20"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
@@ -21178,7 +21208,7 @@
       <c r="Q216" s="1"/>
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
-      <c r="T216" s="1"/>
+      <c r="T216" s="20"/>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
@@ -21233,7 +21263,7 @@
       <c r="Q217" s="1"/>
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
-      <c r="T217" s="1"/>
+      <c r="T217" s="20"/>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
@@ -21288,7 +21318,7 @@
       <c r="Q218" s="1"/>
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
-      <c r="T218" s="1"/>
+      <c r="T218" s="20"/>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
@@ -21343,7 +21373,7 @@
       <c r="Q219" s="1"/>
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
-      <c r="T219" s="1"/>
+      <c r="T219" s="20"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
@@ -21398,7 +21428,7 @@
       <c r="Q220" s="1"/>
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
-      <c r="T220" s="1"/>
+      <c r="T220" s="20"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
@@ -21453,7 +21483,7 @@
       <c r="Q221" s="1"/>
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
-      <c r="T221" s="1"/>
+      <c r="T221" s="20"/>
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
@@ -21508,7 +21538,7 @@
       <c r="Q222" s="1"/>
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
-      <c r="T222" s="1"/>
+      <c r="T222" s="20"/>
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
@@ -21563,7 +21593,7 @@
       <c r="Q223" s="1"/>
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
-      <c r="T223" s="1"/>
+      <c r="T223" s="20"/>
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
@@ -21618,7 +21648,7 @@
       <c r="Q224" s="1"/>
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
-      <c r="T224" s="1"/>
+      <c r="T224" s="20"/>
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
@@ -21673,7 +21703,7 @@
       <c r="Q225" s="1"/>
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
-      <c r="T225" s="1"/>
+      <c r="T225" s="20"/>
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
@@ -21728,7 +21758,7 @@
       <c r="Q226" s="1"/>
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
-      <c r="T226" s="1"/>
+      <c r="T226" s="20"/>
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
@@ -21783,7 +21813,7 @@
       <c r="Q227" s="1"/>
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
-      <c r="T227" s="1"/>
+      <c r="T227" s="20"/>
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
@@ -21838,7 +21868,7 @@
       <c r="Q228" s="1"/>
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
-      <c r="T228" s="1"/>
+      <c r="T228" s="20"/>
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
@@ -21893,7 +21923,7 @@
       <c r="Q229" s="1"/>
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
-      <c r="T229" s="1"/>
+      <c r="T229" s="20"/>
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
@@ -21948,7 +21978,7 @@
       <c r="Q230" s="1"/>
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
-      <c r="T230" s="1"/>
+      <c r="T230" s="20"/>
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
@@ -22003,7 +22033,7 @@
       <c r="Q231" s="1"/>
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
-      <c r="T231" s="1"/>
+      <c r="T231" s="20"/>
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
@@ -22058,7 +22088,7 @@
       <c r="Q232" s="1"/>
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
-      <c r="T232" s="1"/>
+      <c r="T232" s="20"/>
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
@@ -22113,7 +22143,7 @@
       <c r="Q233" s="1"/>
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
-      <c r="T233" s="1"/>
+      <c r="T233" s="20"/>
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
@@ -22168,7 +22198,7 @@
       <c r="Q234" s="1"/>
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
-      <c r="T234" s="1"/>
+      <c r="T234" s="20"/>
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
@@ -22223,7 +22253,7 @@
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
-      <c r="T235" s="1"/>
+      <c r="T235" s="20"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
@@ -22278,7 +22308,7 @@
       <c r="Q236" s="1"/>
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
-      <c r="T236" s="1"/>
+      <c r="T236" s="20"/>
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
@@ -22333,7 +22363,7 @@
       <c r="Q237" s="1"/>
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
-      <c r="T237" s="1"/>
+      <c r="T237" s="20"/>
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
@@ -22388,7 +22418,7 @@
       <c r="Q238" s="1"/>
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
-      <c r="T238" s="1"/>
+      <c r="T238" s="20"/>
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
@@ -22443,7 +22473,7 @@
       <c r="Q239" s="1"/>
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
-      <c r="T239" s="1"/>
+      <c r="T239" s="20"/>
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
@@ -22498,7 +22528,7 @@
       <c r="Q240" s="1"/>
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
-      <c r="T240" s="1"/>
+      <c r="T240" s="20"/>
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
@@ -22553,7 +22583,7 @@
       <c r="Q241" s="1"/>
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
-      <c r="T241" s="1"/>
+      <c r="T241" s="20"/>
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
@@ -22608,7 +22638,7 @@
       <c r="Q242" s="1"/>
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
-      <c r="T242" s="1"/>
+      <c r="T242" s="20"/>
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
@@ -22663,7 +22693,7 @@
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
-      <c r="T243" s="1"/>
+      <c r="T243" s="20"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
@@ -22718,7 +22748,7 @@
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
-      <c r="T244" s="1"/>
+      <c r="T244" s="20"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
@@ -22773,7 +22803,7 @@
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
       <c r="S245" s="1"/>
-      <c r="T245" s="1"/>
+      <c r="T245" s="20"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
@@ -22828,7 +22858,7 @@
       <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
-      <c r="T246" s="1"/>
+      <c r="T246" s="20"/>
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
@@ -22883,7 +22913,7 @@
       <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
-      <c r="T247" s="1"/>
+      <c r="T247" s="20"/>
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
@@ -22938,7 +22968,7 @@
       <c r="Q248" s="1"/>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
-      <c r="T248" s="1"/>
+      <c r="T248" s="20"/>
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
@@ -22993,7 +23023,7 @@
       <c r="Q249" s="1"/>
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
-      <c r="T249" s="1"/>
+      <c r="T249" s="20"/>
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
@@ -23048,7 +23078,7 @@
       <c r="Q250" s="1"/>
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
-      <c r="T250" s="1"/>
+      <c r="T250" s="20"/>
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
@@ -23103,7 +23133,7 @@
       <c r="Q251" s="1"/>
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
-      <c r="T251" s="1"/>
+      <c r="T251" s="20"/>
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
@@ -23158,7 +23188,7 @@
       <c r="Q252" s="1"/>
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
-      <c r="T252" s="1"/>
+      <c r="T252" s="20"/>
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
@@ -23213,7 +23243,7 @@
       <c r="Q253" s="1"/>
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
-      <c r="T253" s="1"/>
+      <c r="T253" s="20"/>
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
@@ -23268,7 +23298,7 @@
       <c r="Q254" s="1"/>
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
-      <c r="T254" s="1"/>
+      <c r="T254" s="20"/>
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
@@ -23323,7 +23353,7 @@
       <c r="Q255" s="1"/>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
-      <c r="T255" s="1"/>
+      <c r="T255" s="20"/>
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
@@ -23378,7 +23408,7 @@
       <c r="Q256" s="1"/>
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
-      <c r="T256" s="1"/>
+      <c r="T256" s="20"/>
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
@@ -23433,7 +23463,7 @@
       <c r="Q257" s="1"/>
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
-      <c r="T257" s="1"/>
+      <c r="T257" s="20"/>
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
@@ -23488,7 +23518,7 @@
       <c r="Q258" s="1"/>
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
-      <c r="T258" s="1"/>
+      <c r="T258" s="20"/>
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
@@ -23543,7 +23573,7 @@
       <c r="Q259" s="1"/>
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
-      <c r="T259" s="1"/>
+      <c r="T259" s="20"/>
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
@@ -23598,7 +23628,7 @@
       <c r="Q260" s="1"/>
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
-      <c r="T260" s="1"/>
+      <c r="T260" s="20"/>
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
@@ -23653,7 +23683,7 @@
       <c r="Q261" s="1"/>
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
-      <c r="T261" s="1"/>
+      <c r="T261" s="20"/>
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
@@ -23708,7 +23738,7 @@
       <c r="Q262" s="1"/>
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
-      <c r="T262" s="1"/>
+      <c r="T262" s="20"/>
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
@@ -23763,7 +23793,7 @@
       <c r="Q263" s="1"/>
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
-      <c r="T263" s="1"/>
+      <c r="T263" s="20"/>
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
@@ -23818,7 +23848,7 @@
       <c r="Q264" s="1"/>
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
-      <c r="T264" s="1"/>
+      <c r="T264" s="20"/>
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
@@ -23873,7 +23903,7 @@
       <c r="Q265" s="1"/>
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
-      <c r="T265" s="1"/>
+      <c r="T265" s="20"/>
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
@@ -23928,7 +23958,7 @@
       <c r="Q266" s="1"/>
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
-      <c r="T266" s="1"/>
+      <c r="T266" s="20"/>
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
@@ -23983,7 +24013,7 @@
       <c r="Q267" s="1"/>
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
-      <c r="T267" s="1"/>
+      <c r="T267" s="20"/>
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
@@ -24038,7 +24068,7 @@
       <c r="Q268" s="1"/>
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
-      <c r="T268" s="1"/>
+      <c r="T268" s="20"/>
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
@@ -24093,7 +24123,7 @@
       <c r="Q269" s="1"/>
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
-      <c r="T269" s="1"/>
+      <c r="T269" s="20"/>
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
@@ -24148,7 +24178,7 @@
       <c r="Q270" s="1"/>
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
-      <c r="T270" s="1"/>
+      <c r="T270" s="20"/>
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
@@ -24203,7 +24233,7 @@
       <c r="Q271" s="1"/>
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
-      <c r="T271" s="1"/>
+      <c r="T271" s="20"/>
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
@@ -24258,7 +24288,7 @@
       <c r="Q272" s="1"/>
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
-      <c r="T272" s="1"/>
+      <c r="T272" s="20"/>
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
@@ -24313,7 +24343,7 @@
       <c r="Q273" s="1"/>
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
-      <c r="T273" s="1"/>
+      <c r="T273" s="20"/>
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
@@ -24368,7 +24398,7 @@
       <c r="Q274" s="1"/>
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
-      <c r="T274" s="1"/>
+      <c r="T274" s="20"/>
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
@@ -24423,7 +24453,7 @@
       <c r="Q275" s="1"/>
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
-      <c r="T275" s="1"/>
+      <c r="T275" s="20"/>
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
@@ -24478,7 +24508,7 @@
       <c r="Q276" s="1"/>
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
+      <c r="T276" s="20"/>
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
@@ -24533,7 +24563,7 @@
       <c r="Q277" s="1"/>
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
+      <c r="T277" s="20"/>
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
@@ -24588,7 +24618,7 @@
       <c r="Q278" s="1"/>
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
+      <c r="T278" s="20"/>
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
@@ -24643,7 +24673,7 @@
       <c r="Q279" s="1"/>
       <c r="R279" s="1"/>
       <c r="S279" s="1"/>
-      <c r="T279" s="1"/>
+      <c r="T279" s="20"/>
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
@@ -24698,7 +24728,7 @@
       <c r="Q280" s="1"/>
       <c r="R280" s="1"/>
       <c r="S280" s="1"/>
-      <c r="T280" s="1"/>
+      <c r="T280" s="20"/>
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
@@ -24753,7 +24783,7 @@
       <c r="Q281" s="1"/>
       <c r="R281" s="1"/>
       <c r="S281" s="1"/>
-      <c r="T281" s="1"/>
+      <c r="T281" s="20"/>
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
       <c r="W281" s="1"/>
@@ -24808,7 +24838,7 @@
       <c r="Q282" s="1"/>
       <c r="R282" s="1"/>
       <c r="S282" s="1"/>
-      <c r="T282" s="1"/>
+      <c r="T282" s="20"/>
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
       <c r="W282" s="1"/>
@@ -24863,7 +24893,7 @@
       <c r="Q283" s="1"/>
       <c r="R283" s="1"/>
       <c r="S283" s="1"/>
-      <c r="T283" s="1"/>
+      <c r="T283" s="20"/>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
@@ -24918,7 +24948,7 @@
       <c r="Q284" s="1"/>
       <c r="R284" s="1"/>
       <c r="S284" s="1"/>
-      <c r="T284" s="1"/>
+      <c r="T284" s="20"/>
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
       <c r="W284" s="1"/>
@@ -24973,7 +25003,7 @@
       <c r="Q285" s="1"/>
       <c r="R285" s="1"/>
       <c r="S285" s="1"/>
-      <c r="T285" s="1"/>
+      <c r="T285" s="20"/>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
@@ -25028,7 +25058,7 @@
       <c r="Q286" s="1"/>
       <c r="R286" s="1"/>
       <c r="S286" s="1"/>
-      <c r="T286" s="1"/>
+      <c r="T286" s="20"/>
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
       <c r="W286" s="1"/>
@@ -25083,7 +25113,7 @@
       <c r="Q287" s="1"/>
       <c r="R287" s="1"/>
       <c r="S287" s="1"/>
-      <c r="T287" s="1"/>
+      <c r="T287" s="20"/>
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
       <c r="W287" s="1"/>
@@ -25138,7 +25168,7 @@
       <c r="Q288" s="1"/>
       <c r="R288" s="1"/>
       <c r="S288" s="1"/>
-      <c r="T288" s="1"/>
+      <c r="T288" s="20"/>
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
       <c r="W288" s="1"/>
@@ -25193,7 +25223,7 @@
       <c r="Q289" s="1"/>
       <c r="R289" s="1"/>
       <c r="S289" s="1"/>
-      <c r="T289" s="1"/>
+      <c r="T289" s="20"/>
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
       <c r="W289" s="1"/>
@@ -25248,7 +25278,7 @@
       <c r="Q290" s="1"/>
       <c r="R290" s="1"/>
       <c r="S290" s="1"/>
-      <c r="T290" s="1"/>
+      <c r="T290" s="20"/>
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
       <c r="W290" s="1"/>
@@ -25303,7 +25333,7 @@
       <c r="Q291" s="1"/>
       <c r="R291" s="1"/>
       <c r="S291" s="1"/>
-      <c r="T291" s="1"/>
+      <c r="T291" s="20"/>
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
       <c r="W291" s="1"/>
@@ -25358,7 +25388,7 @@
       <c r="Q292" s="1"/>
       <c r="R292" s="1"/>
       <c r="S292" s="1"/>
-      <c r="T292" s="1"/>
+      <c r="T292" s="20"/>
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
       <c r="W292" s="1"/>
@@ -25413,7 +25443,7 @@
       <c r="Q293" s="1"/>
       <c r="R293" s="1"/>
       <c r="S293" s="1"/>
-      <c r="T293" s="1"/>
+      <c r="T293" s="20"/>
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
       <c r="W293" s="1"/>
@@ -25468,7 +25498,7 @@
       <c r="Q294" s="1"/>
       <c r="R294" s="1"/>
       <c r="S294" s="1"/>
-      <c r="T294" s="1"/>
+      <c r="T294" s="20"/>
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
       <c r="W294" s="1"/>
@@ -25523,7 +25553,7 @@
       <c r="Q295" s="1"/>
       <c r="R295" s="1"/>
       <c r="S295" s="1"/>
-      <c r="T295" s="1"/>
+      <c r="T295" s="20"/>
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
       <c r="W295" s="1"/>
@@ -25578,7 +25608,7 @@
       <c r="Q296" s="1"/>
       <c r="R296" s="1"/>
       <c r="S296" s="1"/>
-      <c r="T296" s="1"/>
+      <c r="T296" s="20"/>
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
       <c r="W296" s="1"/>
@@ -25633,7 +25663,7 @@
       <c r="Q297" s="1"/>
       <c r="R297" s="1"/>
       <c r="S297" s="1"/>
-      <c r="T297" s="1"/>
+      <c r="T297" s="20"/>
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
       <c r="W297" s="1"/>
@@ -25688,7 +25718,7 @@
       <c r="Q298" s="1"/>
       <c r="R298" s="1"/>
       <c r="S298" s="1"/>
-      <c r="T298" s="1"/>
+      <c r="T298" s="20"/>
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
       <c r="W298" s="1"/>
@@ -25743,7 +25773,7 @@
       <c r="Q299" s="1"/>
       <c r="R299" s="1"/>
       <c r="S299" s="1"/>
-      <c r="T299" s="1"/>
+      <c r="T299" s="20"/>
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
       <c r="W299" s="1"/>
@@ -25798,7 +25828,7 @@
       <c r="Q300" s="1"/>
       <c r="R300" s="1"/>
       <c r="S300" s="1"/>
-      <c r="T300" s="1"/>
+      <c r="T300" s="20"/>
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
       <c r="W300" s="1"/>
@@ -25853,7 +25883,7 @@
       <c r="Q301" s="1"/>
       <c r="R301" s="1"/>
       <c r="S301" s="1"/>
-      <c r="T301" s="1"/>
+      <c r="T301" s="20"/>
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
       <c r="W301" s="1"/>
@@ -25908,7 +25938,7 @@
       <c r="Q302" s="1"/>
       <c r="R302" s="1"/>
       <c r="S302" s="1"/>
-      <c r="T302" s="1"/>
+      <c r="T302" s="20"/>
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
       <c r="W302" s="1"/>
@@ -25963,7 +25993,7 @@
       <c r="Q303" s="1"/>
       <c r="R303" s="1"/>
       <c r="S303" s="1"/>
-      <c r="T303" s="1"/>
+      <c r="T303" s="20"/>
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
       <c r="W303" s="1"/>
@@ -26018,7 +26048,7 @@
       <c r="Q304" s="1"/>
       <c r="R304" s="1"/>
       <c r="S304" s="1"/>
-      <c r="T304" s="1"/>
+      <c r="T304" s="20"/>
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
       <c r="W304" s="1"/>
@@ -26073,7 +26103,7 @@
       <c r="Q305" s="1"/>
       <c r="R305" s="1"/>
       <c r="S305" s="1"/>
-      <c r="T305" s="1"/>
+      <c r="T305" s="20"/>
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
       <c r="W305" s="1"/>
@@ -26128,7 +26158,7 @@
       <c r="Q306" s="1"/>
       <c r="R306" s="1"/>
       <c r="S306" s="1"/>
-      <c r="T306" s="1"/>
+      <c r="T306" s="20"/>
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
       <c r="W306" s="1"/>
@@ -26183,7 +26213,7 @@
       <c r="Q307" s="1"/>
       <c r="R307" s="1"/>
       <c r="S307" s="1"/>
-      <c r="T307" s="1"/>
+      <c r="T307" s="20"/>
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
       <c r="W307" s="1"/>
@@ -26238,7 +26268,7 @@
       <c r="Q308" s="1"/>
       <c r="R308" s="1"/>
       <c r="S308" s="1"/>
-      <c r="T308" s="1"/>
+      <c r="T308" s="20"/>
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
       <c r="W308" s="1"/>
@@ -26293,7 +26323,7 @@
       <c r="Q309" s="1"/>
       <c r="R309" s="1"/>
       <c r="S309" s="1"/>
-      <c r="T309" s="1"/>
+      <c r="T309" s="20"/>
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
@@ -26348,7 +26378,7 @@
       <c r="Q310" s="1"/>
       <c r="R310" s="1"/>
       <c r="S310" s="1"/>
-      <c r="T310" s="1"/>
+      <c r="T310" s="20"/>
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
       <c r="W310" s="1"/>
@@ -26403,7 +26433,7 @@
       <c r="Q311" s="1"/>
       <c r="R311" s="1"/>
       <c r="S311" s="1"/>
-      <c r="T311" s="1"/>
+      <c r="T311" s="20"/>
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
       <c r="W311" s="1"/>
@@ -26458,7 +26488,7 @@
       <c r="Q312" s="1"/>
       <c r="R312" s="1"/>
       <c r="S312" s="1"/>
-      <c r="T312" s="1"/>
+      <c r="T312" s="20"/>
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
       <c r="W312" s="1"/>
@@ -26513,7 +26543,7 @@
       <c r="Q313" s="1"/>
       <c r="R313" s="1"/>
       <c r="S313" s="1"/>
-      <c r="T313" s="1"/>
+      <c r="T313" s="20"/>
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
       <c r="W313" s="1"/>
@@ -26568,7 +26598,7 @@
       <c r="Q314" s="1"/>
       <c r="R314" s="1"/>
       <c r="S314" s="1"/>
-      <c r="T314" s="1"/>
+      <c r="T314" s="20"/>
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
       <c r="W314" s="1"/>
@@ -26623,7 +26653,7 @@
       <c r="Q315" s="1"/>
       <c r="R315" s="1"/>
       <c r="S315" s="1"/>
-      <c r="T315" s="1"/>
+      <c r="T315" s="20"/>
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
       <c r="W315" s="1"/>
@@ -26678,7 +26708,7 @@
       <c r="Q316" s="1"/>
       <c r="R316" s="1"/>
       <c r="S316" s="1"/>
-      <c r="T316" s="1"/>
+      <c r="T316" s="20"/>
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
       <c r="W316" s="1"/>
@@ -26733,7 +26763,7 @@
       <c r="Q317" s="1"/>
       <c r="R317" s="1"/>
       <c r="S317" s="1"/>
-      <c r="T317" s="1"/>
+      <c r="T317" s="20"/>
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
       <c r="W317" s="1"/>
@@ -26788,7 +26818,7 @@
       <c r="Q318" s="1"/>
       <c r="R318" s="1"/>
       <c r="S318" s="1"/>
-      <c r="T318" s="1"/>
+      <c r="T318" s="20"/>
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
       <c r="W318" s="1"/>
@@ -26843,7 +26873,7 @@
       <c r="Q319" s="1"/>
       <c r="R319" s="1"/>
       <c r="S319" s="1"/>
-      <c r="T319" s="1"/>
+      <c r="T319" s="20"/>
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
       <c r="W319" s="1"/>
@@ -26898,7 +26928,7 @@
       <c r="Q320" s="1"/>
       <c r="R320" s="1"/>
       <c r="S320" s="1"/>
-      <c r="T320" s="1"/>
+      <c r="T320" s="20"/>
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
       <c r="W320" s="1"/>
@@ -26953,7 +26983,7 @@
       <c r="Q321" s="1"/>
       <c r="R321" s="1"/>
       <c r="S321" s="1"/>
-      <c r="T321" s="1"/>
+      <c r="T321" s="20"/>
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
       <c r="W321" s="1"/>
@@ -27008,7 +27038,7 @@
       <c r="Q322" s="1"/>
       <c r="R322" s="1"/>
       <c r="S322" s="1"/>
-      <c r="T322" s="1"/>
+      <c r="T322" s="20"/>
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
       <c r="W322" s="1"/>
@@ -27063,7 +27093,7 @@
       <c r="Q323" s="1"/>
       <c r="R323" s="1"/>
       <c r="S323" s="1"/>
-      <c r="T323" s="1"/>
+      <c r="T323" s="20"/>
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
       <c r="W323" s="1"/>
@@ -27118,7 +27148,7 @@
       <c r="Q324" s="1"/>
       <c r="R324" s="1"/>
       <c r="S324" s="1"/>
-      <c r="T324" s="1"/>
+      <c r="T324" s="20"/>
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
       <c r="W324" s="1"/>
@@ -27173,7 +27203,7 @@
       <c r="Q325" s="1"/>
       <c r="R325" s="1"/>
       <c r="S325" s="1"/>
-      <c r="T325" s="1"/>
+      <c r="T325" s="20"/>
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
       <c r="W325" s="1"/>
@@ -27228,7 +27258,7 @@
       <c r="Q326" s="1"/>
       <c r="R326" s="1"/>
       <c r="S326" s="1"/>
-      <c r="T326" s="1"/>
+      <c r="T326" s="20"/>
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
       <c r="W326" s="1"/>
@@ -27283,7 +27313,7 @@
       <c r="Q327" s="1"/>
       <c r="R327" s="1"/>
       <c r="S327" s="1"/>
-      <c r="T327" s="1"/>
+      <c r="T327" s="20"/>
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
       <c r="W327" s="1"/>
@@ -27338,7 +27368,7 @@
       <c r="Q328" s="1"/>
       <c r="R328" s="1"/>
       <c r="S328" s="1"/>
-      <c r="T328" s="1"/>
+      <c r="T328" s="20"/>
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
       <c r="W328" s="1"/>
@@ -27393,7 +27423,7 @@
       <c r="Q329" s="1"/>
       <c r="R329" s="1"/>
       <c r="S329" s="1"/>
-      <c r="T329" s="1"/>
+      <c r="T329" s="20"/>
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
       <c r="W329" s="1"/>
@@ -27448,7 +27478,7 @@
       <c r="Q330" s="1"/>
       <c r="R330" s="1"/>
       <c r="S330" s="1"/>
-      <c r="T330" s="1"/>
+      <c r="T330" s="20"/>
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
       <c r="W330" s="1"/>
@@ -27503,7 +27533,7 @@
       <c r="Q331" s="1"/>
       <c r="R331" s="1"/>
       <c r="S331" s="1"/>
-      <c r="T331" s="1"/>
+      <c r="T331" s="20"/>
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
       <c r="W331" s="1"/>
@@ -27558,7 +27588,7 @@
       <c r="Q332" s="1"/>
       <c r="R332" s="1"/>
       <c r="S332" s="1"/>
-      <c r="T332" s="1"/>
+      <c r="T332" s="20"/>
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
       <c r="W332" s="1"/>
@@ -27613,7 +27643,7 @@
       <c r="Q333" s="1"/>
       <c r="R333" s="1"/>
       <c r="S333" s="1"/>
-      <c r="T333" s="1"/>
+      <c r="T333" s="20"/>
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
       <c r="W333" s="1"/>
@@ -27668,7 +27698,7 @@
       <c r="Q334" s="1"/>
       <c r="R334" s="1"/>
       <c r="S334" s="1"/>
-      <c r="T334" s="1"/>
+      <c r="T334" s="20"/>
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
       <c r="W334" s="1"/>
@@ -27723,7 +27753,7 @@
       <c r="Q335" s="1"/>
       <c r="R335" s="1"/>
       <c r="S335" s="1"/>
-      <c r="T335" s="1"/>
+      <c r="T335" s="20"/>
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
       <c r="W335" s="1"/>
@@ -27778,7 +27808,7 @@
       <c r="Q336" s="1"/>
       <c r="R336" s="1"/>
       <c r="S336" s="1"/>
-      <c r="T336" s="1"/>
+      <c r="T336" s="20"/>
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
       <c r="W336" s="1"/>
@@ -27833,7 +27863,7 @@
       <c r="Q337" s="1"/>
       <c r="R337" s="1"/>
       <c r="S337" s="1"/>
-      <c r="T337" s="1"/>
+      <c r="T337" s="20"/>
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
       <c r="W337" s="1"/>
@@ -27888,7 +27918,7 @@
       <c r="Q338" s="1"/>
       <c r="R338" s="1"/>
       <c r="S338" s="1"/>
-      <c r="T338" s="1"/>
+      <c r="T338" s="20"/>
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
       <c r="W338" s="1"/>
@@ -27943,7 +27973,7 @@
       <c r="Q339" s="1"/>
       <c r="R339" s="1"/>
       <c r="S339" s="1"/>
-      <c r="T339" s="1"/>
+      <c r="T339" s="20"/>
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
       <c r="W339" s="1"/>
@@ -27998,7 +28028,7 @@
       <c r="Q340" s="1"/>
       <c r="R340" s="1"/>
       <c r="S340" s="1"/>
-      <c r="T340" s="1"/>
+      <c r="T340" s="20"/>
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
       <c r="W340" s="1"/>
@@ -28053,7 +28083,7 @@
       <c r="Q341" s="1"/>
       <c r="R341" s="1"/>
       <c r="S341" s="1"/>
-      <c r="T341" s="1"/>
+      <c r="T341" s="20"/>
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
@@ -28108,7 +28138,7 @@
       <c r="Q342" s="1"/>
       <c r="R342" s="1"/>
       <c r="S342" s="1"/>
-      <c r="T342" s="1"/>
+      <c r="T342" s="20"/>
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
       <c r="W342" s="1"/>
@@ -28163,7 +28193,7 @@
       <c r="Q343" s="1"/>
       <c r="R343" s="1"/>
       <c r="S343" s="1"/>
-      <c r="T343" s="1"/>
+      <c r="T343" s="20"/>
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
       <c r="W343" s="1"/>
@@ -28218,7 +28248,7 @@
       <c r="Q344" s="1"/>
       <c r="R344" s="1"/>
       <c r="S344" s="1"/>
-      <c r="T344" s="1"/>
+      <c r="T344" s="20"/>
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
       <c r="W344" s="1"/>
@@ -28273,7 +28303,7 @@
       <c r="Q345" s="1"/>
       <c r="R345" s="1"/>
       <c r="S345" s="1"/>
-      <c r="T345" s="1"/>
+      <c r="T345" s="20"/>
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
       <c r="W345" s="1"/>
@@ -28328,7 +28358,7 @@
       <c r="Q346" s="1"/>
       <c r="R346" s="1"/>
       <c r="S346" s="1"/>
-      <c r="T346" s="1"/>
+      <c r="T346" s="20"/>
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
       <c r="W346" s="1"/>
@@ -28383,7 +28413,7 @@
       <c r="Q347" s="1"/>
       <c r="R347" s="1"/>
       <c r="S347" s="1"/>
-      <c r="T347" s="1"/>
+      <c r="T347" s="20"/>
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
       <c r="W347" s="1"/>
@@ -28438,7 +28468,7 @@
       <c r="Q348" s="1"/>
       <c r="R348" s="1"/>
       <c r="S348" s="1"/>
-      <c r="T348" s="1"/>
+      <c r="T348" s="20"/>
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
       <c r="W348" s="1"/>
@@ -28493,7 +28523,7 @@
       <c r="Q349" s="1"/>
       <c r="R349" s="1"/>
       <c r="S349" s="1"/>
-      <c r="T349" s="1"/>
+      <c r="T349" s="20"/>
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
       <c r="W349" s="1"/>
@@ -28548,7 +28578,7 @@
       <c r="Q350" s="1"/>
       <c r="R350" s="1"/>
       <c r="S350" s="1"/>
-      <c r="T350" s="1"/>
+      <c r="T350" s="20"/>
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
       <c r="W350" s="1"/>
@@ -28603,7 +28633,7 @@
       <c r="Q351" s="1"/>
       <c r="R351" s="1"/>
       <c r="S351" s="1"/>
-      <c r="T351" s="1"/>
+      <c r="T351" s="20"/>
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
       <c r="W351" s="1"/>
@@ -28658,7 +28688,7 @@
       <c r="Q352" s="1"/>
       <c r="R352" s="1"/>
       <c r="S352" s="1"/>
-      <c r="T352" s="1"/>
+      <c r="T352" s="20"/>
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
       <c r="W352" s="1"/>
@@ -28713,7 +28743,7 @@
       <c r="Q353" s="1"/>
       <c r="R353" s="1"/>
       <c r="S353" s="1"/>
-      <c r="T353" s="1"/>
+      <c r="T353" s="20"/>
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
       <c r="W353" s="1"/>
@@ -28768,7 +28798,7 @@
       <c r="Q354" s="1"/>
       <c r="R354" s="1"/>
       <c r="S354" s="1"/>
-      <c r="T354" s="1"/>
+      <c r="T354" s="20"/>
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
       <c r="W354" s="1"/>
@@ -28823,7 +28853,7 @@
       <c r="Q355" s="1"/>
       <c r="R355" s="1"/>
       <c r="S355" s="1"/>
-      <c r="T355" s="1"/>
+      <c r="T355" s="20"/>
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
       <c r="W355" s="1"/>
@@ -28878,7 +28908,7 @@
       <c r="Q356" s="1"/>
       <c r="R356" s="1"/>
       <c r="S356" s="1"/>
-      <c r="T356" s="1"/>
+      <c r="T356" s="20"/>
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
       <c r="W356" s="1"/>
@@ -28933,7 +28963,7 @@
       <c r="Q357" s="1"/>
       <c r="R357" s="1"/>
       <c r="S357" s="1"/>
-      <c r="T357" s="1"/>
+      <c r="T357" s="20"/>
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
       <c r="W357" s="1"/>
@@ -28988,7 +29018,7 @@
       <c r="Q358" s="1"/>
       <c r="R358" s="1"/>
       <c r="S358" s="1"/>
-      <c r="T358" s="1"/>
+      <c r="T358" s="20"/>
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
       <c r="W358" s="1"/>
@@ -29043,7 +29073,7 @@
       <c r="Q359" s="1"/>
       <c r="R359" s="1"/>
       <c r="S359" s="1"/>
-      <c r="T359" s="1"/>
+      <c r="T359" s="20"/>
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
       <c r="W359" s="1"/>
@@ -29098,7 +29128,7 @@
       <c r="Q360" s="1"/>
       <c r="R360" s="1"/>
       <c r="S360" s="1"/>
-      <c r="T360" s="1"/>
+      <c r="T360" s="20"/>
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
       <c r="W360" s="1"/>
@@ -29153,7 +29183,7 @@
       <c r="Q361" s="1"/>
       <c r="R361" s="1"/>
       <c r="S361" s="1"/>
-      <c r="T361" s="1"/>
+      <c r="T361" s="20"/>
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
       <c r="W361" s="1"/>
@@ -29208,7 +29238,7 @@
       <c r="Q362" s="1"/>
       <c r="R362" s="1"/>
       <c r="S362" s="1"/>
-      <c r="T362" s="1"/>
+      <c r="T362" s="20"/>
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
       <c r="W362" s="1"/>
@@ -29263,7 +29293,7 @@
       <c r="Q363" s="1"/>
       <c r="R363" s="1"/>
       <c r="S363" s="1"/>
-      <c r="T363" s="1"/>
+      <c r="T363" s="20"/>
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
       <c r="W363" s="1"/>
@@ -29318,7 +29348,7 @@
       <c r="Q364" s="1"/>
       <c r="R364" s="1"/>
       <c r="S364" s="1"/>
-      <c r="T364" s="1"/>
+      <c r="T364" s="20"/>
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
       <c r="W364" s="1"/>
@@ -29373,7 +29403,7 @@
       <c r="Q365" s="1"/>
       <c r="R365" s="1"/>
       <c r="S365" s="1"/>
-      <c r="T365" s="1"/>
+      <c r="T365" s="20"/>
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
       <c r="W365" s="1"/>
@@ -29428,7 +29458,7 @@
       <c r="Q366" s="1"/>
       <c r="R366" s="1"/>
       <c r="S366" s="1"/>
-      <c r="T366" s="1"/>
+      <c r="T366" s="20"/>
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
       <c r="W366" s="1"/>
@@ -29483,7 +29513,7 @@
       <c r="Q367" s="1"/>
       <c r="R367" s="1"/>
       <c r="S367" s="1"/>
-      <c r="T367" s="1"/>
+      <c r="T367" s="20"/>
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
       <c r="W367" s="1"/>
@@ -29538,7 +29568,7 @@
       <c r="Q368" s="1"/>
       <c r="R368" s="1"/>
       <c r="S368" s="1"/>
-      <c r="T368" s="1"/>
+      <c r="T368" s="20"/>
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
       <c r="W368" s="1"/>
@@ -29593,7 +29623,7 @@
       <c r="Q369" s="1"/>
       <c r="R369" s="1"/>
       <c r="S369" s="1"/>
-      <c r="T369" s="1"/>
+      <c r="T369" s="20"/>
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
       <c r="W369" s="1"/>
@@ -29648,7 +29678,7 @@
       <c r="Q370" s="1"/>
       <c r="R370" s="1"/>
       <c r="S370" s="1"/>
-      <c r="T370" s="1"/>
+      <c r="T370" s="20"/>
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
       <c r="W370" s="1"/>
@@ -29703,7 +29733,7 @@
       <c r="Q371" s="1"/>
       <c r="R371" s="1"/>
       <c r="S371" s="1"/>
-      <c r="T371" s="1"/>
+      <c r="T371" s="20"/>
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
       <c r="W371" s="1"/>
@@ -29758,7 +29788,7 @@
       <c r="Q372" s="1"/>
       <c r="R372" s="1"/>
       <c r="S372" s="1"/>
-      <c r="T372" s="1"/>
+      <c r="T372" s="20"/>
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
       <c r="W372" s="1"/>
@@ -29813,7 +29843,7 @@
       <c r="Q373" s="1"/>
       <c r="R373" s="1"/>
       <c r="S373" s="1"/>
-      <c r="T373" s="1"/>
+      <c r="T373" s="20"/>
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
       <c r="W373" s="1"/>
@@ -29868,7 +29898,7 @@
       <c r="Q374" s="1"/>
       <c r="R374" s="1"/>
       <c r="S374" s="1"/>
-      <c r="T374" s="1"/>
+      <c r="T374" s="20"/>
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
       <c r="W374" s="1"/>
@@ -29923,7 +29953,7 @@
       <c r="Q375" s="1"/>
       <c r="R375" s="1"/>
       <c r="S375" s="1"/>
-      <c r="T375" s="1"/>
+      <c r="T375" s="20"/>
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
       <c r="W375" s="1"/>
@@ -29978,7 +30008,7 @@
       <c r="Q376" s="1"/>
       <c r="R376" s="1"/>
       <c r="S376" s="1"/>
-      <c r="T376" s="1"/>
+      <c r="T376" s="20"/>
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
       <c r="W376" s="1"/>
@@ -30033,7 +30063,7 @@
       <c r="Q377" s="1"/>
       <c r="R377" s="1"/>
       <c r="S377" s="1"/>
-      <c r="T377" s="1"/>
+      <c r="T377" s="20"/>
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
       <c r="W377" s="1"/>
@@ -30088,7 +30118,7 @@
       <c r="Q378" s="1"/>
       <c r="R378" s="1"/>
       <c r="S378" s="1"/>
-      <c r="T378" s="1"/>
+      <c r="T378" s="20"/>
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
       <c r="W378" s="1"/>
@@ -30143,7 +30173,7 @@
       <c r="Q379" s="1"/>
       <c r="R379" s="1"/>
       <c r="S379" s="1"/>
-      <c r="T379" s="1"/>
+      <c r="T379" s="20"/>
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
       <c r="W379" s="1"/>
@@ -30198,7 +30228,7 @@
       <c r="Q380" s="1"/>
       <c r="R380" s="1"/>
       <c r="S380" s="1"/>
-      <c r="T380" s="1"/>
+      <c r="T380" s="20"/>
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
       <c r="W380" s="1"/>
@@ -30253,7 +30283,7 @@
       <c r="Q381" s="1"/>
       <c r="R381" s="1"/>
       <c r="S381" s="1"/>
-      <c r="T381" s="1"/>
+      <c r="T381" s="20"/>
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
       <c r="W381" s="1"/>
@@ -30308,7 +30338,7 @@
       <c r="Q382" s="1"/>
       <c r="R382" s="1"/>
       <c r="S382" s="1"/>
-      <c r="T382" s="1"/>
+      <c r="T382" s="20"/>
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
       <c r="W382" s="1"/>
@@ -30363,7 +30393,7 @@
       <c r="Q383" s="1"/>
       <c r="R383" s="1"/>
       <c r="S383" s="1"/>
-      <c r="T383" s="1"/>
+      <c r="T383" s="20"/>
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
       <c r="W383" s="1"/>
@@ -30418,7 +30448,7 @@
       <c r="Q384" s="1"/>
       <c r="R384" s="1"/>
       <c r="S384" s="1"/>
-      <c r="T384" s="1"/>
+      <c r="T384" s="20"/>
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
       <c r="W384" s="1"/>
@@ -30473,7 +30503,7 @@
       <c r="Q385" s="1"/>
       <c r="R385" s="1"/>
       <c r="S385" s="1"/>
-      <c r="T385" s="1"/>
+      <c r="T385" s="20"/>
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
       <c r="W385" s="1"/>
@@ -30528,7 +30558,7 @@
       <c r="Q386" s="1"/>
       <c r="R386" s="1"/>
       <c r="S386" s="1"/>
-      <c r="T386" s="1"/>
+      <c r="T386" s="20"/>
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
       <c r="W386" s="1"/>
@@ -30583,7 +30613,7 @@
       <c r="Q387" s="1"/>
       <c r="R387" s="1"/>
       <c r="S387" s="1"/>
-      <c r="T387" s="1"/>
+      <c r="T387" s="20"/>
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
       <c r="W387" s="1"/>
@@ -30638,7 +30668,7 @@
       <c r="Q388" s="1"/>
       <c r="R388" s="1"/>
       <c r="S388" s="1"/>
-      <c r="T388" s="1"/>
+      <c r="T388" s="20"/>
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
       <c r="W388" s="1"/>
@@ -30693,7 +30723,7 @@
       <c r="Q389" s="1"/>
       <c r="R389" s="1"/>
       <c r="S389" s="1"/>
-      <c r="T389" s="1"/>
+      <c r="T389" s="20"/>
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
       <c r="W389" s="1"/>
@@ -30748,7 +30778,7 @@
       <c r="Q390" s="1"/>
       <c r="R390" s="1"/>
       <c r="S390" s="1"/>
-      <c r="T390" s="1"/>
+      <c r="T390" s="20"/>
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
       <c r="W390" s="1"/>
@@ -30803,7 +30833,7 @@
       <c r="Q391" s="1"/>
       <c r="R391" s="1"/>
       <c r="S391" s="1"/>
-      <c r="T391" s="1"/>
+      <c r="T391" s="20"/>
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
       <c r="W391" s="1"/>
@@ -30858,7 +30888,7 @@
       <c r="Q392" s="1"/>
       <c r="R392" s="1"/>
       <c r="S392" s="1"/>
-      <c r="T392" s="1"/>
+      <c r="T392" s="20"/>
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
       <c r="W392" s="1"/>
@@ -30913,7 +30943,7 @@
       <c r="Q393" s="1"/>
       <c r="R393" s="1"/>
       <c r="S393" s="1"/>
-      <c r="T393" s="1"/>
+      <c r="T393" s="20"/>
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
       <c r="W393" s="1"/>
@@ -30968,7 +30998,7 @@
       <c r="Q394" s="1"/>
       <c r="R394" s="1"/>
       <c r="S394" s="1"/>
-      <c r="T394" s="1"/>
+      <c r="T394" s="20"/>
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
       <c r="W394" s="1"/>
@@ -31023,7 +31053,7 @@
       <c r="Q395" s="1"/>
       <c r="R395" s="1"/>
       <c r="S395" s="1"/>
-      <c r="T395" s="1"/>
+      <c r="T395" s="20"/>
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
       <c r="W395" s="1"/>
@@ -31078,7 +31108,7 @@
       <c r="Q396" s="1"/>
       <c r="R396" s="1"/>
       <c r="S396" s="1"/>
-      <c r="T396" s="1"/>
+      <c r="T396" s="20"/>
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
       <c r="W396" s="1"/>
@@ -31133,7 +31163,7 @@
       <c r="Q397" s="1"/>
       <c r="R397" s="1"/>
       <c r="S397" s="1"/>
-      <c r="T397" s="1"/>
+      <c r="T397" s="20"/>
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
       <c r="W397" s="1"/>
@@ -31188,7 +31218,7 @@
       <c r="Q398" s="1"/>
       <c r="R398" s="1"/>
       <c r="S398" s="1"/>
-      <c r="T398" s="1"/>
+      <c r="T398" s="20"/>
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
       <c r="W398" s="1"/>
@@ -31243,7 +31273,7 @@
       <c r="Q399" s="1"/>
       <c r="R399" s="1"/>
       <c r="S399" s="1"/>
-      <c r="T399" s="1"/>
+      <c r="T399" s="20"/>
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
       <c r="W399" s="1"/>
@@ -31298,7 +31328,7 @@
       <c r="Q400" s="1"/>
       <c r="R400" s="1"/>
       <c r="S400" s="1"/>
-      <c r="T400" s="1"/>
+      <c r="T400" s="20"/>
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
       <c r="W400" s="1"/>
@@ -31353,7 +31383,7 @@
       <c r="Q401" s="1"/>
       <c r="R401" s="1"/>
       <c r="S401" s="1"/>
-      <c r="T401" s="1"/>
+      <c r="T401" s="20"/>
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
       <c r="W401" s="1"/>
@@ -31408,7 +31438,7 @@
       <c r="Q402" s="1"/>
       <c r="R402" s="1"/>
       <c r="S402" s="1"/>
-      <c r="T402" s="1"/>
+      <c r="T402" s="20"/>
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
       <c r="W402" s="1"/>
@@ -31463,7 +31493,7 @@
       <c r="Q403" s="1"/>
       <c r="R403" s="1"/>
       <c r="S403" s="1"/>
-      <c r="T403" s="1"/>
+      <c r="T403" s="20"/>
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
       <c r="W403" s="1"/>
@@ -31518,7 +31548,7 @@
       <c r="Q404" s="1"/>
       <c r="R404" s="1"/>
       <c r="S404" s="1"/>
-      <c r="T404" s="1"/>
+      <c r="T404" s="20"/>
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
       <c r="W404" s="1"/>
@@ -31573,7 +31603,7 @@
       <c r="Q405" s="1"/>
       <c r="R405" s="1"/>
       <c r="S405" s="1"/>
-      <c r="T405" s="1"/>
+      <c r="T405" s="20"/>
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
       <c r="W405" s="1"/>
@@ -31628,7 +31658,7 @@
       <c r="Q406" s="1"/>
       <c r="R406" s="1"/>
       <c r="S406" s="1"/>
-      <c r="T406" s="1"/>
+      <c r="T406" s="20"/>
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
       <c r="W406" s="1"/>
@@ -31683,7 +31713,7 @@
       <c r="Q407" s="1"/>
       <c r="R407" s="1"/>
       <c r="S407" s="1"/>
-      <c r="T407" s="1"/>
+      <c r="T407" s="20"/>
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
       <c r="W407" s="1"/>
@@ -31738,7 +31768,7 @@
       <c r="Q408" s="1"/>
       <c r="R408" s="1"/>
       <c r="S408" s="1"/>
-      <c r="T408" s="1"/>
+      <c r="T408" s="20"/>
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
       <c r="W408" s="1"/>
@@ -31793,7 +31823,7 @@
       <c r="Q409" s="1"/>
       <c r="R409" s="1"/>
       <c r="S409" s="1"/>
-      <c r="T409" s="1"/>
+      <c r="T409" s="20"/>
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
       <c r="W409" s="1"/>
@@ -31848,7 +31878,7 @@
       <c r="Q410" s="1"/>
       <c r="R410" s="1"/>
       <c r="S410" s="1"/>
-      <c r="T410" s="1"/>
+      <c r="T410" s="20"/>
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
       <c r="W410" s="1"/>
@@ -31903,7 +31933,7 @@
       <c r="Q411" s="1"/>
       <c r="R411" s="1"/>
       <c r="S411" s="1"/>
-      <c r="T411" s="1"/>
+      <c r="T411" s="20"/>
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
       <c r="W411" s="1"/>
@@ -31958,7 +31988,7 @@
       <c r="Q412" s="1"/>
       <c r="R412" s="1"/>
       <c r="S412" s="1"/>
-      <c r="T412" s="1"/>
+      <c r="T412" s="20"/>
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
       <c r="W412" s="1"/>
@@ -32013,7 +32043,7 @@
       <c r="Q413" s="1"/>
       <c r="R413" s="1"/>
       <c r="S413" s="1"/>
-      <c r="T413" s="1"/>
+      <c r="T413" s="20"/>
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
       <c r="W413" s="1"/>
@@ -32068,7 +32098,7 @@
       <c r="Q414" s="1"/>
       <c r="R414" s="1"/>
       <c r="S414" s="1"/>
-      <c r="T414" s="1"/>
+      <c r="T414" s="20"/>
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
       <c r="W414" s="1"/>
@@ -32123,7 +32153,7 @@
       <c r="Q415" s="1"/>
       <c r="R415" s="1"/>
       <c r="S415" s="1"/>
-      <c r="T415" s="1"/>
+      <c r="T415" s="20"/>
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
       <c r="W415" s="1"/>
@@ -32178,7 +32208,7 @@
       <c r="Q416" s="1"/>
       <c r="R416" s="1"/>
       <c r="S416" s="1"/>
-      <c r="T416" s="1"/>
+      <c r="T416" s="20"/>
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
       <c r="W416" s="1"/>
@@ -32233,7 +32263,7 @@
       <c r="Q417" s="1"/>
       <c r="R417" s="1"/>
       <c r="S417" s="1"/>
-      <c r="T417" s="1"/>
+      <c r="T417" s="20"/>
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
       <c r="W417" s="1"/>
@@ -32288,7 +32318,7 @@
       <c r="Q418" s="1"/>
       <c r="R418" s="1"/>
       <c r="S418" s="1"/>
-      <c r="T418" s="1"/>
+      <c r="T418" s="20"/>
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
       <c r="W418" s="1"/>
@@ -32343,7 +32373,7 @@
       <c r="Q419" s="1"/>
       <c r="R419" s="1"/>
       <c r="S419" s="1"/>
-      <c r="T419" s="1"/>
+      <c r="T419" s="20"/>
       <c r="U419" s="1"/>
       <c r="V419" s="1"/>
       <c r="W419" s="1"/>
@@ -32398,7 +32428,7 @@
       <c r="Q420" s="1"/>
       <c r="R420" s="1"/>
       <c r="S420" s="1"/>
-      <c r="T420" s="1"/>
+      <c r="T420" s="20"/>
       <c r="U420" s="1"/>
       <c r="V420" s="1"/>
       <c r="W420" s="1"/>
@@ -32453,7 +32483,7 @@
       <c r="Q421" s="1"/>
       <c r="R421" s="1"/>
       <c r="S421" s="1"/>
-      <c r="T421" s="1"/>
+      <c r="T421" s="20"/>
       <c r="U421" s="1"/>
       <c r="V421" s="1"/>
       <c r="W421" s="1"/>
@@ -32508,7 +32538,7 @@
       <c r="Q422" s="1"/>
       <c r="R422" s="1"/>
       <c r="S422" s="1"/>
-      <c r="T422" s="1"/>
+      <c r="T422" s="20"/>
       <c r="U422" s="1"/>
       <c r="V422" s="1"/>
       <c r="W422" s="1"/>
@@ -32563,7 +32593,7 @@
       <c r="Q423" s="1"/>
       <c r="R423" s="1"/>
       <c r="S423" s="1"/>
-      <c r="T423" s="1"/>
+      <c r="T423" s="20"/>
       <c r="U423" s="1"/>
       <c r="V423" s="1"/>
       <c r="W423" s="1"/>
@@ -32618,7 +32648,7 @@
       <c r="Q424" s="1"/>
       <c r="R424" s="1"/>
       <c r="S424" s="1"/>
-      <c r="T424" s="1"/>
+      <c r="T424" s="20"/>
       <c r="U424" s="1"/>
       <c r="V424" s="1"/>
       <c r="W424" s="1"/>
@@ -32673,7 +32703,7 @@
       <c r="Q425" s="1"/>
       <c r="R425" s="1"/>
       <c r="S425" s="1"/>
-      <c r="T425" s="1"/>
+      <c r="T425" s="20"/>
       <c r="U425" s="1"/>
       <c r="V425" s="1"/>
       <c r="W425" s="1"/>
@@ -32728,7 +32758,7 @@
       <c r="Q426" s="1"/>
       <c r="R426" s="1"/>
       <c r="S426" s="1"/>
-      <c r="T426" s="1"/>
+      <c r="T426" s="20"/>
       <c r="U426" s="1"/>
       <c r="V426" s="1"/>
       <c r="W426" s="1"/>
@@ -32783,7 +32813,7 @@
       <c r="Q427" s="1"/>
       <c r="R427" s="1"/>
       <c r="S427" s="1"/>
-      <c r="T427" s="1"/>
+      <c r="T427" s="20"/>
       <c r="U427" s="1"/>
       <c r="V427" s="1"/>
       <c r="W427" s="1"/>
@@ -32838,7 +32868,7 @@
       <c r="Q428" s="1"/>
       <c r="R428" s="1"/>
       <c r="S428" s="1"/>
-      <c r="T428" s="1"/>
+      <c r="T428" s="20"/>
       <c r="U428" s="1"/>
       <c r="V428" s="1"/>
       <c r="W428" s="1"/>
@@ -32893,7 +32923,7 @@
       <c r="Q429" s="1"/>
       <c r="R429" s="1"/>
       <c r="S429" s="1"/>
-      <c r="T429" s="1"/>
+      <c r="T429" s="20"/>
       <c r="U429" s="1"/>
       <c r="V429" s="1"/>
       <c r="W429" s="1"/>
@@ -32948,7 +32978,7 @@
       <c r="Q430" s="1"/>
       <c r="R430" s="1"/>
       <c r="S430" s="1"/>
-      <c r="T430" s="1"/>
+      <c r="T430" s="20"/>
       <c r="U430" s="1"/>
       <c r="V430" s="1"/>
       <c r="W430" s="1"/>
@@ -33003,7 +33033,7 @@
       <c r="Q431" s="1"/>
       <c r="R431" s="1"/>
       <c r="S431" s="1"/>
-      <c r="T431" s="1"/>
+      <c r="T431" s="20"/>
       <c r="U431" s="1"/>
       <c r="V431" s="1"/>
       <c r="W431" s="1"/>
@@ -33058,7 +33088,7 @@
       <c r="Q432" s="1"/>
       <c r="R432" s="1"/>
       <c r="S432" s="1"/>
-      <c r="T432" s="1"/>
+      <c r="T432" s="20"/>
       <c r="U432" s="1"/>
       <c r="V432" s="1"/>
       <c r="W432" s="1"/>
@@ -33113,7 +33143,7 @@
       <c r="Q433" s="1"/>
       <c r="R433" s="1"/>
       <c r="S433" s="1"/>
-      <c r="T433" s="1"/>
+      <c r="T433" s="20"/>
       <c r="U433" s="1"/>
       <c r="V433" s="1"/>
       <c r="W433" s="1"/>
@@ -33168,7 +33198,7 @@
       <c r="Q434" s="1"/>
       <c r="R434" s="1"/>
       <c r="S434" s="1"/>
-      <c r="T434" s="1"/>
+      <c r="T434" s="20"/>
       <c r="U434" s="1"/>
       <c r="V434" s="1"/>
       <c r="W434" s="1"/>
@@ -33223,7 +33253,7 @@
       <c r="Q435" s="1"/>
       <c r="R435" s="1"/>
       <c r="S435" s="1"/>
-      <c r="T435" s="1"/>
+      <c r="T435" s="20"/>
       <c r="U435" s="1"/>
       <c r="V435" s="1"/>
       <c r="W435" s="1"/>
@@ -33278,7 +33308,7 @@
       <c r="Q436" s="1"/>
       <c r="R436" s="1"/>
       <c r="S436" s="1"/>
-      <c r="T436" s="1"/>
+      <c r="T436" s="20"/>
       <c r="U436" s="1"/>
       <c r="V436" s="1"/>
       <c r="W436" s="1"/>
@@ -33333,7 +33363,7 @@
       <c r="Q437" s="1"/>
       <c r="R437" s="1"/>
       <c r="S437" s="1"/>
-      <c r="T437" s="1"/>
+      <c r="T437" s="20"/>
       <c r="U437" s="1"/>
       <c r="V437" s="1"/>
       <c r="W437" s="1"/>
@@ -33388,7 +33418,7 @@
       <c r="Q438" s="1"/>
       <c r="R438" s="1"/>
       <c r="S438" s="1"/>
-      <c r="T438" s="1"/>
+      <c r="T438" s="20"/>
       <c r="U438" s="1"/>
       <c r="V438" s="1"/>
       <c r="W438" s="1"/>
@@ -33443,7 +33473,7 @@
       <c r="Q439" s="1"/>
       <c r="R439" s="1"/>
       <c r="S439" s="1"/>
-      <c r="T439" s="1"/>
+      <c r="T439" s="20"/>
       <c r="U439" s="1"/>
       <c r="V439" s="1"/>
       <c r="W439" s="1"/>
@@ -33498,7 +33528,7 @@
       <c r="Q440" s="1"/>
       <c r="R440" s="1"/>
       <c r="S440" s="1"/>
-      <c r="T440" s="1"/>
+      <c r="T440" s="20"/>
       <c r="U440" s="1"/>
       <c r="V440" s="1"/>
       <c r="W440" s="1"/>
@@ -33553,7 +33583,7 @@
       <c r="Q441" s="1"/>
       <c r="R441" s="1"/>
       <c r="S441" s="1"/>
-      <c r="T441" s="1"/>
+      <c r="T441" s="20"/>
       <c r="U441" s="1"/>
       <c r="V441" s="1"/>
       <c r="W441" s="1"/>
@@ -33608,7 +33638,7 @@
       <c r="Q442" s="1"/>
       <c r="R442" s="1"/>
       <c r="S442" s="1"/>
-      <c r="T442" s="1"/>
+      <c r="T442" s="20"/>
       <c r="U442" s="1"/>
       <c r="V442" s="1"/>
       <c r="W442" s="1"/>
@@ -33663,7 +33693,7 @@
       <c r="Q443" s="1"/>
       <c r="R443" s="1"/>
       <c r="S443" s="1"/>
-      <c r="T443" s="1"/>
+      <c r="T443" s="20"/>
       <c r="U443" s="1"/>
       <c r="V443" s="1"/>
       <c r="W443" s="1"/>
@@ -33718,7 +33748,7 @@
       <c r="Q444" s="1"/>
       <c r="R444" s="1"/>
       <c r="S444" s="1"/>
-      <c r="T444" s="1"/>
+      <c r="T444" s="20"/>
       <c r="U444" s="1"/>
       <c r="V444" s="1"/>
       <c r="W444" s="1"/>
@@ -33773,7 +33803,7 @@
       <c r="Q445" s="1"/>
       <c r="R445" s="1"/>
       <c r="S445" s="1"/>
-      <c r="T445" s="1"/>
+      <c r="T445" s="20"/>
       <c r="U445" s="1"/>
       <c r="V445" s="1"/>
       <c r="W445" s="1"/>
@@ -33828,7 +33858,7 @@
       <c r="Q446" s="1"/>
       <c r="R446" s="1"/>
       <c r="S446" s="1"/>
-      <c r="T446" s="1"/>
+      <c r="T446" s="20"/>
       <c r="U446" s="1"/>
       <c r="V446" s="1"/>
       <c r="W446" s="1"/>
@@ -33883,7 +33913,7 @@
       <c r="Q447" s="1"/>
       <c r="R447" s="1"/>
       <c r="S447" s="1"/>
-      <c r="T447" s="1"/>
+      <c r="T447" s="20"/>
       <c r="U447" s="1"/>
       <c r="V447" s="1"/>
       <c r="W447" s="1"/>
@@ -33938,7 +33968,7 @@
       <c r="Q448" s="1"/>
       <c r="R448" s="1"/>
       <c r="S448" s="1"/>
-      <c r="T448" s="1"/>
+      <c r="T448" s="20"/>
       <c r="U448" s="1"/>
       <c r="V448" s="1"/>
       <c r="W448" s="1"/>
@@ -33993,7 +34023,7 @@
       <c r="Q449" s="1"/>
       <c r="R449" s="1"/>
       <c r="S449" s="1"/>
-      <c r="T449" s="1"/>
+      <c r="T449" s="20"/>
       <c r="U449" s="1"/>
       <c r="V449" s="1"/>
       <c r="W449" s="1"/>
@@ -34048,7 +34078,7 @@
       <c r="Q450" s="1"/>
       <c r="R450" s="1"/>
       <c r="S450" s="1"/>
-      <c r="T450" s="1"/>
+      <c r="T450" s="20"/>
       <c r="U450" s="1"/>
       <c r="V450" s="1"/>
       <c r="W450" s="1"/>
@@ -34103,7 +34133,7 @@
       <c r="Q451" s="1"/>
       <c r="R451" s="1"/>
       <c r="S451" s="1"/>
-      <c r="T451" s="1"/>
+      <c r="T451" s="20"/>
       <c r="U451" s="1"/>
       <c r="V451" s="1"/>
       <c r="W451" s="1"/>
@@ -34158,7 +34188,7 @@
       <c r="Q452" s="1"/>
       <c r="R452" s="1"/>
       <c r="S452" s="1"/>
-      <c r="T452" s="1"/>
+      <c r="T452" s="20"/>
       <c r="U452" s="1"/>
       <c r="V452" s="1"/>
       <c r="W452" s="1"/>
@@ -34213,7 +34243,7 @@
       <c r="Q453" s="1"/>
       <c r="R453" s="1"/>
       <c r="S453" s="1"/>
-      <c r="T453" s="1"/>
+      <c r="T453" s="20"/>
       <c r="U453" s="1"/>
       <c r="V453" s="1"/>
       <c r="W453" s="1"/>
@@ -34268,7 +34298,7 @@
       <c r="Q454" s="1"/>
       <c r="R454" s="1"/>
       <c r="S454" s="1"/>
-      <c r="T454" s="1"/>
+      <c r="T454" s="20"/>
       <c r="U454" s="1"/>
       <c r="V454" s="1"/>
       <c r="W454" s="1"/>
@@ -34323,7 +34353,7 @@
       <c r="Q455" s="1"/>
       <c r="R455" s="1"/>
       <c r="S455" s="1"/>
-      <c r="T455" s="1"/>
+      <c r="T455" s="20"/>
       <c r="U455" s="1"/>
       <c r="V455" s="1"/>
       <c r="W455" s="1"/>
@@ -34378,7 +34408,7 @@
       <c r="Q456" s="1"/>
       <c r="R456" s="1"/>
       <c r="S456" s="1"/>
-      <c r="T456" s="1"/>
+      <c r="T456" s="20"/>
       <c r="U456" s="1"/>
       <c r="V456" s="1"/>
       <c r="W456" s="1"/>
@@ -34433,7 +34463,7 @@
       <c r="Q457" s="1"/>
       <c r="R457" s="1"/>
       <c r="S457" s="1"/>
-      <c r="T457" s="1"/>
+      <c r="T457" s="20"/>
       <c r="U457" s="1"/>
       <c r="V457" s="1"/>
       <c r="W457" s="1"/>
@@ -34488,7 +34518,7 @@
       <c r="Q458" s="1"/>
       <c r="R458" s="1"/>
       <c r="S458" s="1"/>
-      <c r="T458" s="1"/>
+      <c r="T458" s="20"/>
       <c r="U458" s="1"/>
       <c r="V458" s="1"/>
       <c r="W458" s="1"/>
@@ -34543,7 +34573,7 @@
       <c r="Q459" s="1"/>
       <c r="R459" s="1"/>
       <c r="S459" s="1"/>
-      <c r="T459" s="1"/>
+      <c r="T459" s="20"/>
       <c r="U459" s="1"/>
       <c r="V459" s="1"/>
       <c r="W459" s="1"/>
@@ -34598,7 +34628,7 @@
       <c r="Q460" s="1"/>
       <c r="R460" s="1"/>
       <c r="S460" s="1"/>
-      <c r="T460" s="1"/>
+      <c r="T460" s="20"/>
       <c r="U460" s="1"/>
       <c r="V460" s="1"/>
       <c r="W460" s="1"/>
@@ -34653,7 +34683,7 @@
       <c r="Q461" s="1"/>
       <c r="R461" s="1"/>
       <c r="S461" s="1"/>
-      <c r="T461" s="1"/>
+      <c r="T461" s="20"/>
       <c r="U461" s="1"/>
       <c r="V461" s="1"/>
       <c r="W461" s="1"/>
@@ -34708,7 +34738,7 @@
       <c r="Q462" s="1"/>
       <c r="R462" s="1"/>
       <c r="S462" s="1"/>
-      <c r="T462" s="1"/>
+      <c r="T462" s="20"/>
       <c r="U462" s="1"/>
       <c r="V462" s="1"/>
       <c r="W462" s="1"/>
@@ -34763,7 +34793,7 @@
       <c r="Q463" s="1"/>
       <c r="R463" s="1"/>
       <c r="S463" s="1"/>
-      <c r="T463" s="1"/>
+      <c r="T463" s="20"/>
       <c r="U463" s="1"/>
       <c r="V463" s="1"/>
       <c r="W463" s="1"/>
@@ -34818,7 +34848,7 @@
       <c r="Q464" s="1"/>
       <c r="R464" s="1"/>
       <c r="S464" s="1"/>
-      <c r="T464" s="1"/>
+      <c r="T464" s="20"/>
       <c r="U464" s="1"/>
       <c r="V464" s="1"/>
       <c r="W464" s="1"/>
@@ -34873,7 +34903,7 @@
       <c r="Q465" s="1"/>
       <c r="R465" s="1"/>
       <c r="S465" s="1"/>
-      <c r="T465" s="1"/>
+      <c r="T465" s="20"/>
       <c r="U465" s="1"/>
       <c r="V465" s="1"/>
       <c r="W465" s="1"/>
@@ -34928,7 +34958,7 @@
       <c r="Q466" s="1"/>
       <c r="R466" s="1"/>
       <c r="S466" s="1"/>
-      <c r="T466" s="1"/>
+      <c r="T466" s="20"/>
       <c r="U466" s="1"/>
       <c r="V466" s="1"/>
       <c r="W466" s="1"/>
@@ -34983,7 +35013,7 @@
       <c r="Q467" s="1"/>
       <c r="R467" s="1"/>
       <c r="S467" s="1"/>
-      <c r="T467" s="1"/>
+      <c r="T467" s="20"/>
       <c r="U467" s="1"/>
       <c r="V467" s="1"/>
       <c r="W467" s="1"/>
@@ -35038,7 +35068,7 @@
       <c r="Q468" s="1"/>
       <c r="R468" s="1"/>
       <c r="S468" s="1"/>
-      <c r="T468" s="1"/>
+      <c r="T468" s="20"/>
       <c r="U468" s="1"/>
       <c r="V468" s="1"/>
       <c r="W468" s="1"/>
@@ -35093,7 +35123,7 @@
       <c r="Q469" s="1"/>
       <c r="R469" s="1"/>
       <c r="S469" s="1"/>
-      <c r="T469" s="1"/>
+      <c r="T469" s="20"/>
       <c r="U469" s="1"/>
       <c r="V469" s="1"/>
       <c r="W469" s="1"/>
@@ -35148,7 +35178,7 @@
       <c r="Q470" s="1"/>
       <c r="R470" s="1"/>
       <c r="S470" s="1"/>
-      <c r="T470" s="1"/>
+      <c r="T470" s="20"/>
       <c r="U470" s="1"/>
       <c r="V470" s="1"/>
       <c r="W470" s="1"/>
@@ -35203,7 +35233,7 @@
       <c r="Q471" s="1"/>
       <c r="R471" s="1"/>
       <c r="S471" s="1"/>
-      <c r="T471" s="1"/>
+      <c r="T471" s="20"/>
       <c r="U471" s="1"/>
       <c r="V471" s="1"/>
       <c r="W471" s="1"/>
@@ -35258,7 +35288,7 @@
       <c r="Q472" s="1"/>
       <c r="R472" s="1"/>
       <c r="S472" s="1"/>
-      <c r="T472" s="1"/>
+      <c r="T472" s="20"/>
       <c r="U472" s="1"/>
       <c r="V472" s="1"/>
       <c r="W472" s="1"/>
@@ -35313,7 +35343,7 @@
       <c r="Q473" s="1"/>
       <c r="R473" s="1"/>
       <c r="S473" s="1"/>
-      <c r="T473" s="1"/>
+      <c r="T473" s="20"/>
       <c r="U473" s="1"/>
       <c r="V473" s="1"/>
       <c r="W473" s="1"/>
@@ -35368,7 +35398,7 @@
       <c r="Q474" s="1"/>
       <c r="R474" s="1"/>
       <c r="S474" s="1"/>
-      <c r="T474" s="1"/>
+      <c r="T474" s="20"/>
       <c r="U474" s="1"/>
       <c r="V474" s="1"/>
       <c r="W474" s="1"/>
@@ -35423,7 +35453,7 @@
       <c r="Q475" s="1"/>
       <c r="R475" s="1"/>
       <c r="S475" s="1"/>
-      <c r="T475" s="1"/>
+      <c r="T475" s="20"/>
       <c r="U475" s="1"/>
       <c r="V475" s="1"/>
       <c r="W475" s="1"/>
@@ -35478,7 +35508,7 @@
       <c r="Q476" s="1"/>
       <c r="R476" s="1"/>
       <c r="S476" s="1"/>
-      <c r="T476" s="1"/>
+      <c r="T476" s="20"/>
       <c r="U476" s="1"/>
       <c r="V476" s="1"/>
       <c r="W476" s="1"/>
@@ -35533,7 +35563,7 @@
       <c r="Q477" s="1"/>
       <c r="R477" s="1"/>
       <c r="S477" s="1"/>
-      <c r="T477" s="1"/>
+      <c r="T477" s="20"/>
       <c r="U477" s="1"/>
       <c r="V477" s="1"/>
       <c r="W477" s="1"/>
@@ -35588,7 +35618,7 @@
       <c r="Q478" s="1"/>
       <c r="R478" s="1"/>
       <c r="S478" s="1"/>
-      <c r="T478" s="1"/>
+      <c r="T478" s="20"/>
       <c r="U478" s="1"/>
       <c r="V478" s="1"/>
       <c r="W478" s="1"/>
@@ -35643,7 +35673,7 @@
       <c r="Q479" s="1"/>
       <c r="R479" s="1"/>
       <c r="S479" s="1"/>
-      <c r="T479" s="1"/>
+      <c r="T479" s="20"/>
       <c r="U479" s="1"/>
       <c r="V479" s="1"/>
       <c r="W479" s="1"/>
@@ -35698,7 +35728,7 @@
       <c r="Q480" s="1"/>
       <c r="R480" s="1"/>
       <c r="S480" s="1"/>
-      <c r="T480" s="1"/>
+      <c r="T480" s="20"/>
       <c r="U480" s="1"/>
       <c r="V480" s="1"/>
       <c r="W480" s="1"/>
@@ -35753,7 +35783,7 @@
       <c r="Q481" s="1"/>
       <c r="R481" s="1"/>
       <c r="S481" s="1"/>
-      <c r="T481" s="1"/>
+      <c r="T481" s="20"/>
       <c r="U481" s="1"/>
       <c r="V481" s="1"/>
       <c r="W481" s="1"/>
@@ -35808,7 +35838,7 @@
       <c r="Q482" s="1"/>
       <c r="R482" s="1"/>
       <c r="S482" s="1"/>
-      <c r="T482" s="1"/>
+      <c r="T482" s="20"/>
       <c r="U482" s="1"/>
       <c r="V482" s="1"/>
       <c r="W482" s="1"/>
@@ -35863,7 +35893,7 @@
       <c r="Q483" s="1"/>
       <c r="R483" s="1"/>
       <c r="S483" s="1"/>
-      <c r="T483" s="1"/>
+      <c r="T483" s="20"/>
       <c r="U483" s="1"/>
       <c r="V483" s="1"/>
       <c r="W483" s="1"/>
@@ -35918,7 +35948,7 @@
       <c r="Q484" s="1"/>
       <c r="R484" s="1"/>
       <c r="S484" s="1"/>
-      <c r="T484" s="1"/>
+      <c r="T484" s="20"/>
       <c r="U484" s="1"/>
       <c r="V484" s="1"/>
       <c r="W484" s="1"/>
@@ -35973,7 +36003,7 @@
       <c r="Q485" s="1"/>
       <c r="R485" s="1"/>
       <c r="S485" s="1"/>
-      <c r="T485" s="1"/>
+      <c r="T485" s="20"/>
       <c r="U485" s="1"/>
       <c r="V485" s="1"/>
       <c r="W485" s="1"/>
@@ -36028,7 +36058,7 @@
       <c r="Q486" s="1"/>
       <c r="R486" s="1"/>
       <c r="S486" s="1"/>
-      <c r="T486" s="1"/>
+      <c r="T486" s="20"/>
       <c r="U486" s="1"/>
       <c r="V486" s="1"/>
       <c r="W486" s="1"/>
@@ -36083,7 +36113,7 @@
       <c r="Q487" s="1"/>
       <c r="R487" s="1"/>
       <c r="S487" s="1"/>
-      <c r="T487" s="1"/>
+      <c r="T487" s="20"/>
       <c r="U487" s="1"/>
       <c r="V487" s="1"/>
       <c r="W487" s="1"/>
@@ -36138,7 +36168,7 @@
       <c r="Q488" s="1"/>
       <c r="R488" s="1"/>
       <c r="S488" s="1"/>
-      <c r="T488" s="1"/>
+      <c r="T488" s="20"/>
       <c r="U488" s="1"/>
       <c r="V488" s="1"/>
       <c r="W488" s="1"/>
@@ -36193,7 +36223,7 @@
       <c r="Q489" s="1"/>
       <c r="R489" s="1"/>
       <c r="S489" s="1"/>
-      <c r="T489" s="1"/>
+      <c r="T489" s="20"/>
       <c r="U489" s="1"/>
       <c r="V489" s="1"/>
       <c r="W489" s="1"/>
@@ -36248,7 +36278,7 @@
       <c r="Q490" s="1"/>
       <c r="R490" s="1"/>
       <c r="S490" s="1"/>
-      <c r="T490" s="1"/>
+      <c r="T490" s="20"/>
       <c r="U490" s="1"/>
       <c r="V490" s="1"/>
       <c r="W490" s="1"/>
@@ -36303,7 +36333,7 @@
       <c r="Q491" s="1"/>
       <c r="R491" s="1"/>
       <c r="S491" s="1"/>
-      <c r="T491" s="1"/>
+      <c r="T491" s="20"/>
       <c r="U491" s="1"/>
       <c r="V491" s="1"/>
       <c r="W491" s="1"/>
@@ -36358,7 +36388,7 @@
       <c r="Q492" s="1"/>
       <c r="R492" s="1"/>
       <c r="S492" s="1"/>
-      <c r="T492" s="1"/>
+      <c r="T492" s="20"/>
       <c r="U492" s="1"/>
       <c r="V492" s="1"/>
       <c r="W492" s="1"/>
@@ -36413,7 +36443,7 @@
       <c r="Q493" s="1"/>
       <c r="R493" s="1"/>
       <c r="S493" s="1"/>
-      <c r="T493" s="1"/>
+      <c r="T493" s="20"/>
       <c r="U493" s="1"/>
       <c r="V493" s="1"/>
       <c r="W493" s="1"/>
@@ -36468,7 +36498,7 @@
       <c r="Q494" s="1"/>
       <c r="R494" s="1"/>
       <c r="S494" s="1"/>
-      <c r="T494" s="1"/>
+      <c r="T494" s="20"/>
       <c r="U494" s="1"/>
       <c r="V494" s="1"/>
       <c r="W494" s="1"/>
@@ -36523,7 +36553,7 @@
       <c r="Q495" s="1"/>
       <c r="R495" s="1"/>
       <c r="S495" s="1"/>
-      <c r="T495" s="1"/>
+      <c r="T495" s="20"/>
       <c r="U495" s="1"/>
       <c r="V495" s="1"/>
       <c r="W495" s="1"/>
@@ -36578,7 +36608,7 @@
       <c r="Q496" s="1"/>
       <c r="R496" s="1"/>
       <c r="S496" s="1"/>
-      <c r="T496" s="1"/>
+      <c r="T496" s="20"/>
       <c r="U496" s="1"/>
       <c r="V496" s="1"/>
       <c r="W496" s="1"/>
